--- a/data/modelling/atribucion/smartband/df_attr_values_sent.xlsx
+++ b/data/modelling/atribucion/smartband/df_attr_values_sent.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C229"/>
+  <dimension ref="A1:C332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5748.5</v>
+        <v>5850</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03186805410939623</v>
+        <v>-0.6458050313427696</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4959.5</v>
+        <v>5048.5</v>
       </c>
       <c r="C3" t="n">
-        <v>0.610637561704886</v>
+        <v>0.5035998689190384</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29799</v>
+        <v>22059</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2093170554953859</v>
+        <v>-0.2965831438419633</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10189.5</v>
+        <v>10989.5</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3221542949277659</v>
+        <v>-1.482812460203687</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7349</v>
+        <v>7544</v>
       </c>
       <c r="C6" t="n">
-        <v>1.091434248044354</v>
+        <v>0.9666187411719437</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2024.5</v>
+        <v>2019</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2542774001199128</v>
+        <v>-0.7439921539018006</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13539.5</v>
+        <v>16189.5</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2114391678090868</v>
+        <v>-1.442588310737565</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19999.5</v>
+        <v>6614.5</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.9849968069214721</v>
+        <v>1.329029659534716</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11781</v>
+        <v>9530</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.373748859716663</v>
+        <v>0.2423972681990854</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6462</v>
+        <v>1113</v>
       </c>
       <c r="C11" t="n">
-        <v>1.457510522905475</v>
+        <v>0.8729631969689911</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9032.5</v>
+        <v>4119</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.5336464887285345</v>
+        <v>1.247099638280547</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>54499.5</v>
+        <v>8490</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.703187023527472</v>
+        <v>1.225813685305468</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1113</v>
+        <v>3265.5</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9801410132826603</v>
+        <v>0.1203387067938756</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4085.5</v>
+        <v>2565</v>
       </c>
       <c r="C15" t="n">
-        <v>1.345368969500385</v>
+        <v>-1.03923567595869</v>
       </c>
     </row>
     <row r="16">
@@ -634,372 +634,394 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8145</v>
+        <v>13136</v>
       </c>
       <c r="C16" t="n">
-        <v>1.351291376835904</v>
+        <v>-0.8568439891871902</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>precio</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>3339.5</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
       </c>
       <c r="C17" t="n">
-        <v>0.8020838793051366</v>
+        <v>1.66260123571305</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>precio</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2618</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Amazfit</t>
+        </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.6431181836951694</v>
+        <v>1.155394725970234</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>precio</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>15629</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Microwear</t>
+        </is>
       </c>
       <c r="C19" t="n">
-        <v>-1.430007349850531</v>
+        <v>0.4801445504562741</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>precio</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>78499</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-1.648751584751734</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TPU/Aleación de aluminio</t>
+          <t>Smart Bracelet D20</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.368553212327714</v>
+        <v>-0.3057189953712795</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Elastómero termoplástico/Aleación de aluminio</t>
+          <t>Imilab</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.4567147532123107</v>
+        <v>1.046702328999265</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>Noga</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.825706690350366</v>
+        <v>0.9459584906996824</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TPU</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.239497710983832</v>
+        <v>1.806108191583402</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Caucho de silicona</t>
+          <t>DT NO.1</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.02426158379174926</v>
+        <v>0.8808032741798372</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Plástico</t>
+          <t>Honor</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.4497971678037834</v>
+        <v>1.356274694524837</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fluoroelastómero</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.07985780307525252</v>
+        <v>0.7042698623060532</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cuero</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9649523500510054</v>
+        <v>0.1443106094087925</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Acero inoxidable - silicona</t>
+          <t>Mia</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.6107171409654897</v>
+        <v>0.3869011249561403</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Acero inoxidable</t>
+          <t>Haylou</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.275644475881934</v>
+        <v>1.47006170621868</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cuero Genuino</t>
+          <t>Mibro</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.9269666395373191</v>
+        <v>0.6455806871196588</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1ra Metal - 2da Silicona</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>SmartWatches</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1.202431070046421</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Acero inoxidable/Silicona</t>
+          <t>Nictom</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.7710908211366053</v>
+        <v>1.134590918237758</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Silicona / metalica</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>Colmi</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.991743096240287</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Caucho</t>
+          <t>You</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-0.9073157076828384</v>
+        <v>0.9330575454995907</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TPU 24 mm</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>Suono</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.5945334459067199</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1ra Cuero/TPU - 2da Silicona negra</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>Y9</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1.726870864893761</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cartón</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>Netmak</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.07673802310462703</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nailon</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>Smart Band</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.4239476179252585</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Silicona, Metal, Cuero</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>PSP_BAND</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.4669161716180542</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Metal</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>Kingwear</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1.315528107264067</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Resina</t>
+          <t>HiFuture</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -1007,79 +1029,87 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Resina Plastica</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.4012016198194023</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Metal, Cuero y Silicona</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>Genérica</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1.139631848028962</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Goma</t>
+          <t>Ruffo</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.5657675655100373</v>
+        <v>1.442698865934815</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rosa / negra</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>Smartwatches</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.09771295417687101</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Acero</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>Soul</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.6104307573151134</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>simil Cuero</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1087,25 +1117,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PC +TPU</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>Kospet</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.6080679126220291</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Silicona / Tejida Acero Inoxidable</t>
+          <t>RIVERSONG</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1113,27 +1145,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tela</t>
+          <t>JAZAK</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.7723109036172784</v>
+        <v>-0.608027485808223</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Silicona TPU</t>
+          <t>Jazak</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1141,64 +1173,72 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SILICONA Y NYLON</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.6155152690974133</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Polimero de litio</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>Kieslect</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1.90572071820532</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>silicona de alta densidad</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>Geko</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.3995429135065025</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>blanco</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>Belmotec</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1.221460923088486</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Silicona / Tejida de Acero Inoxidable</t>
+          <t>LCS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1206,12 +1246,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tejida de Metal / Caucho</t>
+          <t>ISANFIT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1219,12 +1259,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tela / Metálica</t>
+          <t>FULL-TIME MANIA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1232,133 +1272,147 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BLANCA</t>
+          <t>Integra</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-0.3454858959697423</v>
+        <v>0.9157395322307023</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TPU Silicona</t>
+          <t>Daikon</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-0.9237840634429519</v>
+        <v>-0.781699598380002</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tejida de Acero</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>Aiwa Time</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>-1.047426201502893</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Siliconasilicona</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>Tecnocenter</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.8414881459634237</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Metalica</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>Bazar</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>-1.049850761480375</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>HDT8</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>-1.04502768709632</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Caucho / Tejida metal</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>Goufit</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1.561880903664538</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>Skmei</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.2520945034044504</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Caucho fluorado</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>y68 smart Bracelet</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>-1.045752950288634</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>pllastico siliconado</t>
+          <t>Gen</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1366,25 +1420,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Acero inoxidable Negro</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>DX</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.4008183408395287</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Caucho y Tejida de Acero</t>
+          <t>Smart Bracalet</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1392,761 +1448,815 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Silicona y Acero Inoxidable</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.4014082028210668</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Con malla intercambiable</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>1</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.7071067811865483</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SmartBand</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Con malla intercambiable</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>0</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Smart Tech</t>
+        </is>
       </c>
       <c r="C74" t="n">
-        <v>0.7071067811865466</v>
+        <v>-1.046677447377071</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Peso</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>0.02</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>AIWA TIME</t>
+        </is>
       </c>
       <c r="C75" t="n">
-        <v>0.6064277049626908</v>
+        <v>-1.180704346397499</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Peso</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>0.06</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Y68</t>
+        </is>
       </c>
       <c r="C76" t="n">
-        <v>-1.142089365457693</v>
+        <v>-1.185774699544147</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Peso</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0.780538562499339</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Daza</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Peso</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C78" t="n">
-        <v>0.7964343704062063</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Doogee</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Peso</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-1.041311272410542</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Aiwa time</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Peso</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Mijobs</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.08616283012437173</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Peso</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>0.01</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>dt noN.1</t>
+        </is>
       </c>
       <c r="C81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Peso</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>sw68k</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.6560586285847217</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="C83" t="n">
-        <v>1.905284531027163</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Haxly</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>395</v>
-      </c>
-      <c r="C84" t="n">
-        <v>0.5394834201049772</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Beurer</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>290</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-1.039392822820122</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Solana</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>465</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Targa</t>
+        </is>
       </c>
       <c r="C86" t="n">
-        <v>0.6597490386325776</v>
+        <v>-1.057438071047151</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>260</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-0.8071814269387328</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Generic</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>360</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.4481912158920677</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Garmin Argentina</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>233</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Veryfit</t>
+        </is>
       </c>
       <c r="C89" t="n">
-        <v>-0.03921621493667793</v>
+        <v>-0.8958641060760602</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>325</v>
-      </c>
-      <c r="C90" t="n">
-        <v>0.8016130953330178</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Kolke</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-1.390927548440267</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Gadnic</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>180</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Instto</t>
+        </is>
       </c>
       <c r="C92" t="n">
-        <v>1.632607726590294</v>
+        <v>-0.2962105311463903</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>155</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>T1s</t>
+        </is>
       </c>
       <c r="C93" t="n">
-        <v>-0.6440638123026288</v>
+        <v>-1.339241343394508</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>202.5</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-1.016764728405597</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Evolution</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>110</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>X-time</t>
+        </is>
       </c>
       <c r="C95" t="n">
-        <v>-0.1325487740143658</v>
+        <v>0.3151377771176346</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.0204512679375693</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BlueStar</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>324</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Sweet</t>
+        </is>
       </c>
       <c r="C97" t="n">
-        <v>0.8097042393587537</v>
+        <v>-1.19222427858166</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>504</v>
-      </c>
-      <c r="C98" t="n">
-        <v>1.872157517023741</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Mistral</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>252</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.6822100890644763</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ONCELULAR2</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>192</v>
-      </c>
-      <c r="C100" t="n">
-        <v>0.6121877359167077</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Umidigi</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>120</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.8489477119795004</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Reloj inteligente</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>60</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-0.1894792212832307</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ULI JANUIOT</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>10</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>LEZAYA</t>
+        </is>
       </c>
       <c r="C103" t="n">
-        <v>-0.8356595458176526</v>
+        <v>-1.191168922322732</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>28</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.7377529241543426</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Aiwa</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>94.90000000000001</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>GT1</t>
+        </is>
       </c>
       <c r="C105" t="n">
-        <v>0.7071067811865476</v>
+        <v>-1.045578041997043</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>2372.56</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>aiwa time</t>
+        </is>
       </c>
       <c r="C106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>2752.17</v>
-      </c>
-      <c r="C107" t="inlineStr"/>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>T-Go</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.9609305469954785</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>3701.2</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>IWO</t>
+        </is>
       </c>
       <c r="C108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>3511.39</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Kumi Ku</t>
+        </is>
       </c>
       <c r="C109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>284.71</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.7071067811865476</v>
-      </c>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Reloj Smartband M6</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>3321.58</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
       </c>
       <c r="C111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>4270.61</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>smart Bracelet Y68</t>
+        </is>
       </c>
       <c r="C112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>4460.42</v>
-      </c>
-      <c r="C113" t="inlineStr"/>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>-1.118487373254481</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>1043.92</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>BIP</t>
+        </is>
       </c>
       <c r="C114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>474.51</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>FFRAVEY</t>
+        </is>
       </c>
       <c r="C115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>3891</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Diymore</t>
+        </is>
       </c>
       <c r="C116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>1992.95</v>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Lenovo</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.902624498231231</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>4650.22</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>GOLDI</t>
+        </is>
       </c>
       <c r="C118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>854.12</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>HW 22 PRO</t>
+        </is>
       </c>
       <c r="C119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>2941.98</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>m16 plus</t>
+        </is>
       </c>
       <c r="C120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>3131.78</v>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Tressa</t>
+        </is>
       </c>
       <c r="C121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>AMOLED</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
-        <v>2.057384393797639</v>
-      </c>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LCD IPS</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>0.4374846779698437</v>
-      </c>
+          <t>SKM</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>LCD TFT</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>1.855799577155454</v>
-      </c>
+          <t>SLA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LCD</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.5704205600320786</v>
-      </c>
+          <t>Watch Smart</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LTPS</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>-0.1742515478564544</v>
-      </c>
+          <t>jansin</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>LCD MIP</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.7568393665147223</v>
-      </c>
+          <t>Fitbit</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>LTPO OLED</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.02318211564330171</v>
-      </c>
+          <t>Dinax</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>FitDepot</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>-0.09717595242630335</v>
+        <v>-0.957660880207778</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TFT</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.4356052934806242</v>
-      </c>
+          <t>GTC</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TFT IPS</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -2154,42 +2264,40 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>IPS</t>
+          <t>FitPro</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>-0.0252506123180417</v>
+        <v>-1.18618640083855</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Táctil</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.8057530730375403</v>
-      </c>
+          <t>ANCBIAN ELECTRONICS</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TFT LCD</t>
+          <t>Zafira</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -2197,12 +2305,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>ANC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -2210,12 +2318,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1.14"</t>
+          <t>Riiing</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -2223,27 +2331,25 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PMOLED</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>-1.532539808466068</v>
-      </c>
+          <t>Reloj Inteligente</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>AET</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -2251,282 +2357,252 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SAMOLED</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>0.07034968085219874</v>
-      </c>
+          <t>SMART WATCH BRACELET</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>152 px x 486 px</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>0.7758249221433745</v>
-      </c>
+          <t>Timex</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>126 px x 29 px</t>
+          <t>X-View</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>0.6008323365089945</v>
+        <v>-0.9411774059203626</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>360 px x 360 px</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>1.380101916249138</v>
-      </c>
+          <t>smart bracelet</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>320 px x 385 px</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>0.7665308795723225</v>
-      </c>
+          <t>MIXO</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>454 px x 454 px</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>1.392211590287</v>
-      </c>
+          <t>Smartwatch T80</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>320 px x 360 px</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.5002368554714096</v>
-      </c>
+          <t>JS Watches</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>354 px x 306 px</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>1.514940885773903</v>
-      </c>
+          <t>Noganet</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>194 px x 368 px</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.1234448717569063</v>
-      </c>
+          <t>Repuesto Libre</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>126 px x 294 px</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>1.048398403707732</v>
-      </c>
+          <t>Dala Games</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>320 px x 302 px</t>
+          <t>YOHO</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0.7262356551499416</v>
+        <v>-1.058565445632618</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>208 px x 208 px</t>
+          <t>Dynamic</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>-1.208739493364665</v>
+        <v>-1.107750277281021</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>348 px x 442 px</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>1.610692041343611</v>
-      </c>
+          <t>No Aplica</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>240 px x 240 px</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>0.3837979017074895</v>
-      </c>
+          <t>Smart Bracelet M5</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>480 px x 480 px</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
-        <v>0.394599398945907</v>
-      </c>
+          <t>Electric</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>240 px x 120 px</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
-        <v>0.5753279908286553</v>
-      </c>
+          <t>ROVTOP</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>120 px x 240 px</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
-        <v>-1.01598173687235</v>
-      </c>
+          <t>Smartwatch</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>324 px x 394 px</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>-0.2722782948827837</v>
-      </c>
+          <t>Guess</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>152x486</t>
+          <t>kieselect</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2534,57 +2610,51 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>352 px x 430 px</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.5894337707558264</v>
-      </c>
+          <t>Féraud</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>312 px x 390 px</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.9361849815234129</v>
-      </c>
+          <t>ticwatch</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>390 px x 390 px</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
-        <v>0.07890241925851516</v>
-      </c>
+          <t>VTech</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>400 x 400 px</t>
+          <t>SMART WI598</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2592,27 +2662,25 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>160x 80</t>
-        </is>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.9461202303632726</v>
-      </c>
+          <t>LQ</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>126 x 294</t>
+          <t>Genetica</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2620,42 +2688,38 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>456 px x 280 px</t>
-        </is>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.5688669070989347</v>
-      </c>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>160 px x 80 px</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.8938982298103773</v>
-      </c>
+          <t>Yushu Store</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>466 x 466</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -2663,12 +2727,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>128 px x 128 px</t>
+          <t>DBS</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -2676,42 +2740,38 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>128 x 94 px</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>-1.147431179359417</v>
-      </c>
+          <t>Letsfit</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>126 x 29 px</t>
-        </is>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.2681354650522069</v>
-      </c>
+          <t>Peiso</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>240x240</t>
+          <t>Smart Wristband</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -2719,12 +2779,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>240 * 240 pixeles</t>
+          <t>XI-A</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -2732,12 +2792,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>48 px x 88 px</t>
+          <t>Rovtop</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -2745,730 +2805,2185 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>320 px x 320 px</t>
+          <t>TPU/Aleación de aluminio</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>0.7091303244584054</v>
+        <v>0.3660874167392216</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>240 x 240 px</t>
+          <t>Elastómero termoplástico/Aleación de aluminio</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>-1.29299834199076</v>
+        <v>-0.4534891803446421</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>128 px x 64 px</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>-2.193776307632666</v>
+        <v>1.846871458075724</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>215 px x 180 px</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr"/>
+          <t>TPU</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>2.245703086322948</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>368 px x 448 px</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr"/>
+          <t>Caucho de silicona</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.02401837596183752</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>206 px x 640 px</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr"/>
+          <t>Plástico</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.4466193012921481</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>360 x 360 px</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr"/>
+          <t>Fluoroelastómero</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>0.07938296316935803</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>240 px x 280 px</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr"/>
+          <t>Cuero</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>0.9428164006655914</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Con pantalla táctil</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>1</v>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Acero inoxidable - silicona</t>
+        </is>
       </c>
       <c r="C181" t="n">
-        <v>0.7071067811865476</v>
+        <v>-0.6064295078114287</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Con pantalla táctil</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>0</v>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Acero inoxidable</t>
+        </is>
       </c>
       <c r="C182" t="n">
-        <v>-0.7071067811865476</v>
+        <v>1.266923026590861</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Con red móvil</t>
-        </is>
-      </c>
-      <c r="B183" t="n">
-        <v>0</v>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Cuero Genuino</t>
+        </is>
       </c>
       <c r="C183" t="n">
-        <v>0.7071067811865476</v>
+        <v>-0.9204980269976466</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Con red móvil</t>
-        </is>
-      </c>
-      <c r="B184" t="n">
-        <v>1</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.7071067811865475</v>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1ra Metal - 2da Silicona</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Con GPS</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>0</v>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Acero inoxidable/Silicona</t>
+        </is>
       </c>
       <c r="C185" t="n">
-        <v>0.7071067811865476</v>
+        <v>-0.765697188788783</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Con GPS</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>1</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-0.7071067811865476</v>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Silicona / metalica</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>50000</v>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Caucho</t>
+        </is>
       </c>
       <c r="C187" t="n">
-        <v>1.407370764542204</v>
+        <v>-0.9009826156024116</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>100000</v>
-      </c>
-      <c r="C188" t="n">
-        <v>0.6430254655582368</v>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>TPU 24 mm</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="B189" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C189" t="n">
-        <v>0.6399635001220768</v>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1ra Cuero/TPU - 2da Silicona negra</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-0.8291116170945212</v>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Cartón</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="B191" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-0.7491664867083395</v>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Nailon</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="B192" t="n">
-        <v>0</v>
-      </c>
-      <c r="C192" t="n">
-        <v>0.7908603110137652</v>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Silicona, Metal, Cuero</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="B193" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.445732913148033</v>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>20000</v>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Resina Plastica</t>
+        </is>
       </c>
       <c r="C194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-1.457209024285389</v>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Metal, Cuero y Silicona</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>100</v>
-      </c>
-      <c r="C196" t="inlineStr"/>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Goma</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.5617899220884599</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="B197" t="n">
-        <v>30000</v>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Rosa / negra</t>
+        </is>
       </c>
       <c r="C197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="B198" t="n">
-        <v>2000</v>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>simil Cuero</t>
+        </is>
       </c>
       <c r="C198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="B199" t="n">
-        <v>2500</v>
-      </c>
-      <c r="C199" t="inlineStr"/>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Tela</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>-0.7669088571067425</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="B200" t="n">
-        <v>500</v>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
       </c>
       <c r="C200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="B201" t="n">
-        <v>40000</v>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Silicona TPU</t>
+        </is>
       </c>
       <c r="C201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="B202" t="n">
-        <v>4000</v>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Polimero de litio</t>
+        </is>
       </c>
       <c r="C202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Profundidad máxima de resistencia al agua</t>
-        </is>
-      </c>
-      <c r="B203" t="n">
-        <v>15000</v>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>silicona de alta densidad</t>
+        </is>
       </c>
       <c r="C203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Es resistente al agua</t>
-        </is>
-      </c>
-      <c r="B204" t="n">
-        <v>1</v>
-      </c>
-      <c r="C204" t="n">
-        <v>0.7071067811865476</v>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>blanco</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Es resistente al agua</t>
-        </is>
-      </c>
-      <c r="B205" t="n">
-        <v>0</v>
-      </c>
-      <c r="C205" t="n">
-        <v>-0.7071067811865476</v>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Silicona / Tejida de Acero Inoxidable</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Con micrófono</t>
-        </is>
-      </c>
-      <c r="B206" t="n">
-        <v>0</v>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>BLANCA</t>
+        </is>
       </c>
       <c r="C206" t="n">
-        <v>-0.7071067811865476</v>
+        <v>-0.384013976385343</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Con micrófono</t>
-        </is>
-      </c>
-      <c r="B207" t="n">
-        <v>1</v>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>TPU Silicona</t>
+        </is>
       </c>
       <c r="C207" t="n">
-        <v>0.7071067811865476</v>
+        <v>-0.917337399184261</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Funciones del smartwatch_Aplicacióndeportiva</t>
-        </is>
-      </c>
-      <c r="B208" t="n">
-        <v>1</v>
-      </c>
-      <c r="C208" t="n">
-        <v>0.7071067811865476</v>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Siliconasilicona</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Funciones del smartwatch_Aplicacióndeportiva</t>
-        </is>
-      </c>
-      <c r="B209" t="n">
-        <v>0</v>
-      </c>
-      <c r="C209" t="n">
-        <v>-0.7071067811865476</v>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Metalica</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Funciones del smartwatch_Consumodecalorías</t>
-        </is>
-      </c>
-      <c r="B210" t="n">
-        <v>1</v>
-      </c>
-      <c r="C210" t="n">
-        <v>0.7071067811865475</v>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Funciones del smartwatch_Consumodecalorías</t>
-        </is>
-      </c>
-      <c r="B211" t="n">
-        <v>0</v>
-      </c>
-      <c r="C211" t="n">
-        <v>-0.7071067811865475</v>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Caucho / Tejida metal</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Funciones del smartwatch_Cronómetro</t>
-        </is>
-      </c>
-      <c r="B212" t="n">
-        <v>1</v>
-      </c>
-      <c r="C212" t="n">
-        <v>0.7071067811865476</v>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Silicona y Acero Inoxidable</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Funciones del smartwatch_Cronómetro</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.7071067811865476</v>
+        <v>0.6435396710167419</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Funciones del smartwatch_Cuentapasos</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="C214" t="n">
-        <v>0.7071067811865482</v>
+        <v>-1.138140047596148</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Funciones del smartwatch_Cuentapasos</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.7071067811865468</v>
+        <v>0.7477703344424796</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Funciones del smartwatch_Distanciarecorrida</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="C216" t="n">
-        <v>0.7071067811865485</v>
+        <v>0.7951758189523528</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Funciones del smartwatch_Distanciarecorrida</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.7071067811865466</v>
+        <v>-1.048345776815426</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Sensores_Acelerómetro</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>1</v>
-      </c>
-      <c r="C218" t="n">
-        <v>-0.7071067811865475</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Sensores_Acelerómetro</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0</v>
+        <v>127.5</v>
       </c>
       <c r="C219" t="n">
-        <v>0.7071067811865475</v>
+        <v>1.983890269350773</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Sensores_SensorópticodefrecuenciacardíacaPPG</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>1</v>
+        <v>280</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.707106781186548</v>
+        <v>-0.9729644260180943</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Sensores_SensorópticodefrecuenciacardíacaPPG</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="C221" t="n">
-        <v>0.707106781186547</v>
+        <v>-0.6318549481092582</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Sensores_otros</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>1</v>
+        <v>367.5</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.7071067811865468</v>
+        <v>-0.2137877445400527</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Sensores_otros</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="C223" t="n">
-        <v>0.7071067811865483</v>
+        <v>0.1453624104193269</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Sistemas operativos compatibles del smartwatch_Android</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.7071067811865476</v>
+        <v>0.9632467521614916</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Sistemas operativos compatibles del smartwatch_Android</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>1</v>
+        <v>77.5</v>
       </c>
       <c r="C225" t="n">
-        <v>0.7071067811865476</v>
+        <v>-0.5076793205311546</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Sistemas operativos compatibles del smartwatch_iOS</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0</v>
+        <v>169.5</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.7071067811865454</v>
+        <v>1.663850593413569</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Sistemas operativos compatibles del smartwatch_iOS</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="C227" t="n">
-        <v>0.7071067811865499</v>
+        <v>-1.001836385708082</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Sistemas operativos compatibles del smartwatch_otros</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.7071067811865483</v>
+        <v>-0.3935454282073471</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Sistemas operativos compatibles del smartwatch_otros</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="B229" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="C229" t="n">
+        <v>-0.4747686450574424</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Capacidad de la batería</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>55</v>
+      </c>
+      <c r="C230" t="n">
+        <v>-0.5599131271737287</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Duración de la batería</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>348</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.5865680087353222</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Duración de la batería</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>504</v>
+      </c>
+      <c r="C232" t="n">
+        <v>1.821328404659024</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Duración de la batería</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>252</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0.4723761108903342</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Duración de la batería</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>174</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.329329439930551</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Duración de la batería</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>132</v>
+      </c>
+      <c r="C235" t="n">
+        <v>-1.138418691855499</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Duración de la batería</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>72</v>
+      </c>
+      <c r="C236" t="n">
+        <v>-0.2575920321900372</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Duración de la batería</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>10</v>
+      </c>
+      <c r="C237" t="n">
+        <v>-0.9167046347114906</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Duración de la batería</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>30</v>
+      </c>
+      <c r="C238" t="n">
+        <v>-0.8968866054582043</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>38.812</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0.4216175939067391</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>29.083</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.9264726426687435</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>34.163</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.2830730926979882</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>44.60599999999999</v>
+      </c>
+      <c r="C242" t="n">
+        <v>-1.143743693560441</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>36.449</v>
+      </c>
+      <c r="C243" t="n">
+        <v>1.673835216710329</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>26.343</v>
+      </c>
+      <c r="C244" t="n">
+        <v>1.287139886577272</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>42.545</v>
+      </c>
+      <c r="C245" t="n">
+        <v>-1.346480593323468</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>66</v>
+      </c>
+      <c r="C246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0.8076963039721636</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="C248" t="n">
+        <v>-0.2714166521400362</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>40.767</v>
+      </c>
+      <c r="C249" t="n">
+        <v>-0.03172174225758066</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="C250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="C251" t="n">
+        <v>-0.8739617622312084</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="C252" t="n">
+        <v>-0.4709755498847111</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C253" t="n">
+        <v>-1.261534743135788</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>AMOLED</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>2.026000449472541</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>LCD IPS</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>0.4328279750432226</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>LCD TFT</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>1.891198295466251</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>LCD</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>-0.5679565461556021</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>LTPS</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>-0.1745864154973098</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>LCD MIP</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>-0.7530583284997802</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>LTPO OLED</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>-0.02458426878266995</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>OLED</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>-0.09805534892443135</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>-0.4340937315784523</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>TFT IPS</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>-0.02663815180279872</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>TFT LCD</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Digital</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Táctil</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>-0.8016264661746486</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>1.14"</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>PMOLED</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>-1.537714200544345</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>SAMOLED</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>0.06828673797802398</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>152 px x 486 px</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>0.7837787996425426</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>126 px x 29 px</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>0.6194429891570161</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>360 px x 360 px</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>1.561693579274533</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>320 px x 385 px</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>0.7744326517086563</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>454 px x 454 px</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>1.403621127768818</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>320 px x 360 px</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>-0.5004590227701241</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>354 px x 306 px</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>1.527038482775876</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>194 px x 368 px</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>-0.1224791429421147</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>126 px x 294 px</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>1.053058553138482</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>320 px x 302 px</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>0.7298801357409368</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>208 px x 208 px</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>-1.211195326893922</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>348 px x 442 px</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>1.255530903055381</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>240 px x 240 px</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>0.3879616014805563</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>480 px x 480 px</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>0.3971983439712062</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>240 px x 120 px</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>0.7792549841451376</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>120 px x 240 px</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>-1.0178298711944</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>324 px x 394 px</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>-0.2717817868915035</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>152x486</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>352 px x 430 px</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>-0.589937145387984</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>312 px x 390 px</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>-0.9377815439977422</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>390 px x 390 px</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>0.08050607979947061</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>400 x 400 px</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>160x 80</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>-0.9477481152754286</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>126 x 294</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>456 px x 280 px</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>-0.5693054414519437</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>160 px x 80 px</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>-0.8953614766352663</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>128 px x 128 px</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>128 x 94 px</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>-1.149693728766186</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>126 x 29 px</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>-0.2676258961369492</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>240x240</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>240 * 240 pixeles</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>48 px x 88 px</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>320 px x 320 px</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>0.6457432450449022</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>240 x 240 px</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>-1.295719814820049</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>128 px x 64 px</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>-2.222223163539903</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>368 px x 448 px</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>360 x 360 px</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>240 px x 280 px</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Con pantalla táctil</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>1</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0.7071067811865475</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Con pantalla táctil</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
         <v>0</v>
       </c>
-      <c r="C229" t="n">
-        <v>0.7071067811865467</v>
+      <c r="C311" t="n">
+        <v>-0.7071067811865475</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Con GPS</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>0</v>
+      </c>
+      <c r="C312" t="n">
+        <v>-0.7071067811865475</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Con GPS</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>1</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0.7071067811865476</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Profundidad máxima de resistencia al agua</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>46875</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0.9460771448735934</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Profundidad máxima de resistencia al agua</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>96875</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0.3364123628653204</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Profundidad máxima de resistencia al agua</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>3125</v>
+      </c>
+      <c r="C316" t="n">
+        <v>0.1234038874452978</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Profundidad máxima de resistencia al agua</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>21875</v>
+      </c>
+      <c r="C317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Profundidad máxima de resistencia al agua</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>9375</v>
+      </c>
+      <c r="C318" t="n">
+        <v>-1.405893395184212</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Profundidad máxima de resistencia al agua</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>28125</v>
+      </c>
+      <c r="C319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Profundidad máxima de resistencia al agua</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>40625</v>
+      </c>
+      <c r="C320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Es resistente al agua</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>1</v>
+      </c>
+      <c r="C321" t="n">
+        <v>0.7071067811865476</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Es resistente al agua</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>0</v>
+      </c>
+      <c r="C322" t="n">
+        <v>-0.7071067811865476</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Funciones del smartwatch_Aplicacióndeportiva</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>1</v>
+      </c>
+      <c r="C323" t="n">
+        <v>0.7071067811865475</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Funciones del smartwatch_Aplicacióndeportiva</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>0</v>
+      </c>
+      <c r="C324" t="n">
+        <v>-0.7071067811865475</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Funciones del smartwatch_Calendario</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>1</v>
+      </c>
+      <c r="C325" t="n">
+        <v>0.7071067811865476</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Funciones del smartwatch_Calendario</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>0</v>
+      </c>
+      <c r="C326" t="n">
+        <v>-0.7071067811865476</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Funciones del smartwatch_Consumodecalorías</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>1</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0.7071067811865476</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Funciones del smartwatch_Consumodecalorías</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>0</v>
+      </c>
+      <c r="C328" t="n">
+        <v>-0.7071067811865476</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Funciones del smartwatch_Cronómetro</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>1</v>
+      </c>
+      <c r="C329" t="n">
+        <v>0.7071067811865469</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Funciones del smartwatch_Cronómetro</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>0</v>
+      </c>
+      <c r="C330" t="n">
+        <v>-0.7071067811865482</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Funciones del smartwatch_Cuentapasos</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>1</v>
+      </c>
+      <c r="C331" t="n">
+        <v>0.7071067811865441</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Funciones del smartwatch_Cuentapasos</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>0</v>
+      </c>
+      <c r="C332" t="n">
+        <v>-0.7071067811865509</v>
       </c>
     </row>
   </sheetData>

--- a/data/modelling/atribucion/smartband/df_attr_values_sent.xlsx
+++ b/data/modelling/atribucion/smartband/df_attr_values_sent.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D173"/>
+  <dimension ref="A1:D189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1095</v>
+        <v>5135</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -460,15 +460,15 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.6168365474178787</v>
+        <v>0.1400296842341354</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2199</v>
+        <v>4099</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -476,15 +476,15 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1095703279509695</v>
+        <v>0.1973745530503195</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3321.5</v>
+        <v>14699</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -492,15 +492,15 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="D4" t="n">
-        <v>1.002863192755784</v>
+        <v>-1.095526884265465</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6220</v>
+        <v>7735</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -508,15 +508,15 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="D5" t="n">
-        <v>0.238878573056131</v>
+        <v>0.6349593455072242</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4712.5</v>
+        <v>2167.5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -524,15 +524,15 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6422862665925888</v>
+        <v>-1.182487695691351</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9519.5</v>
+        <v>9327.5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -540,15 +540,15 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="D7" t="n">
-        <v>1.191089005740193</v>
+        <v>1.754890909609559</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15519.5</v>
+        <v>6298.5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -556,15 +556,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.786518962419508</v>
+        <v>-1.012350484243395</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7739.5</v>
+        <v>1119.5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -572,34 +572,32 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7223813328288361</v>
+        <v>-0.3001503667594382</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Suono</t>
-        </is>
+      <c r="A10" t="n">
+        <v>3139.5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>precio</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.454990971732048</v>
+        <v>0.8632609385584101</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Genérica</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -608,16 +606,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4778673416599384</v>
+        <v>1.063104293949428</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Smartwatches</t>
+          <t>Imilab</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -626,16 +624,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9422837416535405</v>
+        <v>1.102815984644837</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Belmotec</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -644,16 +642,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4497707245260589</v>
+        <v>-1.776409596485399</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Amazfit</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -662,16 +660,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>157</v>
+        <v>96</v>
       </c>
       <c r="D14" t="n">
-        <v>1.182423140159567</v>
+        <v>0.7966452242808992</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Imilab</t>
+          <t>Haylou</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -680,16 +678,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>1.156949904018991</v>
+        <v>1.08012981954892</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Microwear</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -698,10 +696,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3938999751931441</v>
+        <v>-0.3535735873121599</v>
       </c>
     </row>
     <row r="17">
@@ -716,10 +714,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5978002568034494</v>
+        <v>-1.055167278614703</v>
       </c>
     </row>
     <row r="18">
@@ -734,16 +732,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6012779025344454</v>
+        <v>0.6548279141237334</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Amazfit</t>
+          <t>Honor</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -752,16 +750,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9342347502158516</v>
+        <v>1.484492854287341</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Microwear</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -770,16 +768,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.90321712225309</v>
+        <v>0.1760685720910358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>DT NO.1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -788,16 +786,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1312646004279692</v>
+        <v>0.7550029798336428</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Honor</t>
+          <t>Noga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -806,16 +804,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>1.514165849141388</v>
+        <v>-0.353720378570089</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -824,16 +822,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5871838983521486</v>
+        <v>1.473592290914306</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mia</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -842,16 +840,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4490581796016619</v>
+        <v>-0.4968093041002776</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DX</t>
+          <t>Nictom</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -860,14 +858,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
+        <v>75</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.3178217137152378</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Geko</t>
+          <t>Shirajo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -876,16 +876,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.187712962755801</v>
+        <v>-0.01681791354602649</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nictom</t>
+          <t>SmartWatches</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2880482292252526</v>
+        <v>0.4794953211555674</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SmartBand</t>
+          <t>You</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -912,14 +912,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.6691890834708132</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Smart Bracalet</t>
+          <t>Suono</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -928,14 +930,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
-      </c>
-      <c r="D29" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-1.043197855406991</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gen</t>
+          <t>Gadnic</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -944,14 +948,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Smart Band</t>
+          <t>Y9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -960,16 +964,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.449890976734728</v>
+        <v>1.45151089479102</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mentedigital</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -978,14 +982,14 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BlueStar</t>
+          <t>PSP_BAND</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -994,14 +998,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-1.096678076763771</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Haylou</t>
+          <t>Kingwear</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1010,16 +1016,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="D34" t="n">
-        <v>1.193449034873089</v>
+        <v>1.187173537787878</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kospet</t>
+          <t>Genérica</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1028,16 +1034,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8565098781134672</v>
+        <v>0.4340865515426019</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Noga</t>
+          <t>Mia</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1046,16 +1052,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.5913044456537938</v>
+        <v>0.3610673833418932</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DT NO.1</t>
+          <t>Kospet</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1064,16 +1070,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9389944139776912</v>
+        <v>-0.9373469967856028</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Ruffo</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1082,14 +1088,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-1.548711301660805</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Aiwa Time</t>
+          <t>Belmotec</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1098,14 +1106,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.8255162515443665</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Libercam</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1114,16 +1124,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>0.678485133126894</v>
+        <v>-1.649054418704722</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Y9</t>
+          <t>Gen</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1132,16 +1142,14 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>126</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1.567290838437035</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PSP_BAND</t>
+          <t>Integra</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1150,16 +1158,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.291522008690654</v>
+        <v>0.7177375010306692</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Goufit</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1168,14 +1176,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.517575608611315</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HiFuture</t>
+          <t>JAZAK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1184,14 +1194,14 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kingwear</t>
+          <t>Geko</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1200,16 +1210,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="D45" t="n">
-        <v>1.17163289643867</v>
+        <v>-0.815465660547558</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ruffo</t>
+          <t>Netmak</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1218,14 +1228,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.203176706140756</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mijobs</t>
+          <t>Aiwa Time</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1234,16 +1246,14 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
-      </c>
-      <c r="D47" t="n">
-        <v>-0.7048553960782357</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SmartWatches</t>
+          <t>y68 smart Bracelet</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1252,16 +1262,14 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>28</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.4629716503530801</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Libercam</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1270,14 +1278,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-0.9073858843636076</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kieslect</t>
+          <t>Smartwatches</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1286,16 +1296,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2763868994013164</v>
+        <v>-1.02364313035354</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Goufit</t>
+          <t>ISANFIT</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1304,16 +1314,14 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
-      </c>
-      <c r="D51" t="n">
-        <v>-0.6115667306390745</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JAZAK</t>
+          <t>Daza</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1322,14 +1330,14 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>aiwa time</t>
+          <t>HDT8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1338,14 +1346,14 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Solana</t>
+          <t>Skmei</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1354,14 +1362,14 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ISANFIT</t>
+          <t>Solana</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1377,7 +1385,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Smart Bracalet</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1386,16 +1394,14 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
-      </c>
-      <c r="D56" t="n">
-        <v>-1.069263889627411</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HDT8</t>
+          <t>SmartBand</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1404,14 +1410,14 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Shirajo</t>
+          <t>mentedigital</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1420,16 +1426,14 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>14</v>
-      </c>
-      <c r="D58" t="n">
-        <v>-0.02360025404836005</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Otras Marcas</t>
+          <t>X-View</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1445,7 +1449,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Netmak</t>
+          <t>Bazar</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1454,16 +1458,14 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>36</v>
-      </c>
-      <c r="D60" t="n">
-        <v>1.387116189376184</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>Soul</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1472,14 +1474,14 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Targa</t>
+          <t>Veryfit</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1488,14 +1490,14 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>Tecnocenter</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1504,14 +1506,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.6917717203323291</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Soul</t>
+          <t>DX</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1520,14 +1524,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-1.176768966351714</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>X-View</t>
+          <t>T-Go</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1536,14 +1542,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
-      </c>
-      <c r="D65" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-0.8120168682791865</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Gadnic</t>
+          <t>Otras Marcas</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1552,14 +1560,14 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Bazar</t>
+          <t>Y68</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1568,14 +1576,14 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mibro</t>
+          <t>sw68k</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1584,14 +1592,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-1.344883772069807</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Doogee</t>
+          <t>AIWA TIME</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1607,7 +1617,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>y68 smart Bracelet</t>
+          <t>BlueStar</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1616,14 +1626,14 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Veryfit</t>
+          <t>Mibro</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1632,14 +1642,14 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>T-Go</t>
+          <t>FULL-TIME MANIA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1648,16 +1658,14 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
-      </c>
-      <c r="D72" t="n">
-        <v>-1.313957306241825</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Integra</t>
+          <t>HiFuture</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1666,16 +1674,14 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>18</v>
-      </c>
-      <c r="D73" t="n">
-        <v>0.8388806688119089</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>Targa</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1691,7 +1697,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Haxly</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1707,7 +1713,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sweet</t>
+          <t>Kieslect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1723,7 +1729,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ONCELULAR2</t>
+          <t>IWO</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1739,7 +1745,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>WickPro</t>
+          <t>aiwa time</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1755,7 +1761,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kolke</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1771,7 +1777,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Umidigi</t>
+          <t>Aiwa time</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1787,7 +1793,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>canta pri</t>
+          <t>Doogee</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1803,7 +1809,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Daza</t>
+          <t>Kolke</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1819,7 +1825,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Rohs</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1835,61 +1841,55 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>Sweet</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>365</v>
-      </c>
-      <c r="D84" t="n">
-        <v>0.936814645318487</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TPU/Aleación de aluminio</t>
+          <t>X8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>14</v>
-      </c>
-      <c r="D85" t="n">
-        <v>-0.3033571376165305</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Fluoroelastómero</t>
+          <t>Rohs</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>21</v>
-      </c>
-      <c r="D86" t="n">
-        <v>0.09294504905282039</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Elastómero termoplástico/Aleación de aluminio</t>
+          <t>TPU/Aleación de aluminio</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1898,16 +1898,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.8660775374209745</v>
+        <v>-0.4109908462209463</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TPU</t>
+          <t>Elastómero termoplástico/Aleación de aluminio</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1916,16 +1916,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.347825198076736</v>
+        <v>-0.8786463318116875</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Plástico</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1934,16 +1934,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>18</v>
+        <v>367</v>
       </c>
       <c r="D89" t="n">
-        <v>-1.005380617283599</v>
+        <v>0.8685263568095842</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Caucho de silicona</t>
+          <t>TPU</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1952,14 +1952,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9</v>
-      </c>
-      <c r="D90" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-0.4955484184498232</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Caucho</t>
+          <t>Fluoroelastómero</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1968,14 +1970,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
-      </c>
-      <c r="D91" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1.115803373946772</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Acero inoxidable</t>
+          <t>Caucho de silicona</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1984,16 +1988,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="D92" t="n">
-        <v>1.976380354841691</v>
+        <v>-0.5877212548313471</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Elastómero termoplástico</t>
+          <t>Plástico</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2002,14 +2006,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="D93" t="n">
+        <v>-0.9162835826786969</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1ra Metal - 2da Silicona</t>
+          <t>Cuero</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2018,14 +2024,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-0.526090141715073</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cuero Genuino</t>
+          <t>Caucho</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2034,14 +2042,14 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Acero inoxidable/Silicona</t>
+          <t>Acero inoxidable</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2050,14 +2058,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>6</v>
-      </c>
-      <c r="D96" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1.830950844951218</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1ra Cuero/TPU - 2da Silicona negra</t>
+          <t>1ra Metal - 2da Silicona</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2073,7 +2083,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>TPU 24 mm</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2089,7 +2099,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Acero inoxidable - silicona</t>
+          <t>Acero inoxidable/Silicona</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2098,14 +2108,14 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Cartón</t>
+          <t>Elastómero termoplástico</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2121,7 +2131,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Rosa / negra</t>
+          <t>Cuero Genuino</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2137,7 +2147,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Band 3 Band 4 Band 5-6</t>
+          <t>1ra Cuero/TPU - 2da Silicona negra</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2153,7 +2163,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cuero</t>
+          <t>Rosa / negra</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2162,16 +2172,14 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>11</v>
-      </c>
-      <c r="D103" t="n">
-        <v>-0.483499558815159</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Nailon</t>
+          <t>Acero inoxidable - silicona</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2180,267 +2188,267 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>Silicona, Metal, Cuero</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>0</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Es resistente al agua</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>91</v>
-      </c>
-      <c r="D106" t="n">
-        <v>-0.7071067811865476</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>1</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Es resistente al agua</t>
-        </is>
-      </c>
       <c r="C107" t="n">
-        <v>541</v>
-      </c>
-      <c r="D107" t="n">
-        <v>0.7071067811865476</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="n">
-        <v>24.638</v>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Nailon</t>
+        </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>32</v>
-      </c>
-      <c r="D108" t="n">
-        <v>-1.361065564527685</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>55.22499999999999</v>
+        <v>0.02</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>17</v>
+        <v>196</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.1129435938667814</v>
+        <v>0.8767838511050374</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>40.058</v>
+        <v>0.06</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D110" t="n">
-        <v>1.085728162550273</v>
+        <v>-1.338508766074603</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>30.099</v>
+        <v>0.04</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D111" t="n">
-        <v>0.4626730201727897</v>
+        <v>0.6389368459429643</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>34.163</v>
+        <v>0.05</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.1968435148854563</v>
+        <v>-0.1772119309733993</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>36.83</v>
+        <v>0</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>58</v>
-      </c>
-      <c r="D113" t="n">
-        <v>1.222179610423064</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>12.52</v>
+        <v>112.5</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>10</v>
-      </c>
-      <c r="D114" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="D114" t="n">
+        <v>1.119757970747649</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>42.955</v>
+        <v>360</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="D115" t="n">
-        <v>-1.099728119866204</v>
+        <v>-0.3954217722000818</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>0.0107</v>
+        <v>251</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D116" t="n">
-        <v>1.027288644219396</v>
+        <v>-0.6826895475654101</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>0.05815000000000001</v>
+        <v>147</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="D117" t="n">
-        <v>0.5439131542123666</v>
+        <v>-0.7211657859987519</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>0.0301</v>
+        <v>215</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>64</v>
+        <v>156</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.08269207894956607</v>
+        <v>0.374409966386717</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>0.0215</v>
+        <v>305</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="D119" t="n">
-        <v>0.1315784433808906</v>
+        <v>-0.2449593766470788</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>0.04</v>
+        <v>175</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="D120" t="n">
-        <v>-1.620088162863087</v>
+        <v>1.733143146896229</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>117.5</v>
+        <v>67.5</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -2448,265 +2456,253 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="D121" t="n">
-        <v>0.9673488355462692</v>
+        <v>-1.183074601619272</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>67.5</v>
+        <v>288</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
+          <t>Duración de la batería</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="D122" t="n">
-        <v>-1.761633103536862</v>
+        <v>1.377902800004959</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>301</v>
+        <v>468</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
+          <t>Duración de la batería</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.1933317227277008</v>
+        <v>0.550924154952558</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>233.5</v>
+        <v>29</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
+          <t>Duración de la batería</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="D124" t="n">
-        <v>0.2182546015656582</v>
+        <v>-0.9367332787406575</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
+          <t>Duración de la batería</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>17</v>
-      </c>
-      <c r="D125" t="inlineStr"/>
+        <v>101</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.4465510650442625</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>190</v>
+        <v>132</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
+          <t>Duración de la batería</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>165</v>
+        <v>44</v>
       </c>
       <c r="D126" t="n">
-        <v>0.9231574067995486</v>
+        <v>-0.1336005875898513</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>382.5</v>
+        <v>60</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
+          <t>Duración de la batería</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.1537960176469136</v>
+        <v>-1.30504415367127</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>276</v>
+        <v>40.31</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="D128" t="n">
-        <v>0.8532079248289963</v>
+        <v>0.8367542873962608</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>468</v>
+        <v>28.46</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="D129" t="n">
-        <v>0.8523437023380049</v>
+        <v>-0.6957555653817187</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>84</v>
+        <v>32.4</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.1493802435766007</v>
+        <v>-0.6440050888914576</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>156</v>
+        <v>44.26</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="D131" t="n">
-        <v>0.03197520263493604</v>
+        <v>0.8711759238939062</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>29</v>
+        <v>36.36</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="D132" t="n">
-        <v>-1.588146586225337</v>
+        <v>0.9504419949783185</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>AMOLED</t>
-        </is>
+      <c r="A133" t="n">
+        <v>24.5</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="D133" t="n">
-        <v>0.9961115788155914</v>
+        <v>-1.31861155199531</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>LCD TFT</t>
-        </is>
+      <c r="A134" t="n">
+        <v>64.03</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>77</v>
-      </c>
-      <c r="D134" t="n">
-        <v>0.6558317280862059</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>LCD IPS</t>
-        </is>
+      <c r="A135" t="n">
+        <v>12.64</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>22</v>
-      </c>
-      <c r="D135" t="n">
-        <v>-0.499484193985648</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>LTPO OLED</t>
-        </is>
+      <c r="A136" t="n">
+        <v>20.54</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>LCD MIP</t>
-        </is>
+      <c r="A137" t="n">
+        <v>60.08</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2717,7 +2713,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TFT</t>
+          <t>AMOLED</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2726,14 +2722,16 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>4</v>
-      </c>
-      <c r="D138" t="inlineStr"/>
+        <v>146</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1.500709363758677</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>LTPS</t>
+          <t>LCD TFT</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2742,14 +2740,16 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
-      </c>
-      <c r="D139" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1.118273604732085</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Táctil</t>
+          <t>SAMOLED</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2758,14 +2758,16 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="D140" t="n">
+        <v>-0.7360139922902258</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>LCD</t>
+          <t>LTPO OLED</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2774,14 +2776,16 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>6</v>
-      </c>
-      <c r="D141" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="D141" t="n">
+        <v>-0.220120477027843</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TFT LCD</t>
+          <t>LCD IPS</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2790,14 +2794,16 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
-      </c>
-      <c r="D142" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.2282393860541106</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>LTPS</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2813,7 +2819,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>LCD MIP</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2829,7 +2835,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SAMOLED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2838,14 +2844,14 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>IPS</t>
+          <t>Táctil</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2854,124 +2860,114 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>7</v>
-      </c>
-      <c r="D146" t="n">
-        <v>-1.15245911291615</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>152 px x 486 px</t>
+          <t>LCD</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D147" t="n">
-        <v>0.5515948595012161</v>
+        <v>-1.128527571745116</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>126 px x 29 px</t>
+          <t>IPS</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.4286842307306204</v>
+        <v>-0.7625603134816871</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>240 px x 240 px</t>
+          <t>TFT IPS</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>60</v>
-      </c>
-      <c r="D149" t="n">
-        <v>-0.06428570718165821</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>320 px x 360 px</t>
+          <t>TFT</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>7</v>
-      </c>
-      <c r="D150" t="n">
-        <v>-0.6541214247505236</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>320 px x 385 px</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>6</v>
-      </c>
-      <c r="D151" t="n">
-        <v>-0.366074671590115</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>360 px x 360 px</t>
+          <t>TFT LCD</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Resolución máxima</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>11</v>
-      </c>
-      <c r="D152" t="n">
-        <v>0.6875293315348678</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>354 px x 306 px</t>
+          <t>152 px x 486 px</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2980,16 +2976,16 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D153" t="n">
-        <v>0.495818074426875</v>
+        <v>0.5357927150182237</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>324 px x 394 px</t>
+          <t>126 px x 29 px</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2998,14 +2994,16 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
-      </c>
-      <c r="D154" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="D154" t="n">
+        <v>-0.3035583087429916</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>194 px x 368 px</t>
+          <t>240 px x 240 px</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3014,16 +3012,16 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="D155" t="n">
-        <v>2.144291378867548</v>
+        <v>-0.1574804054114195</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>208 px x 208 px</t>
+          <t>320 px x 360 px</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3032,14 +3030,16 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>0</v>
-      </c>
-      <c r="D156" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="D156" t="n">
+        <v>-0.8835729108265354</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>160x 80</t>
+          <t>126 px x 294 px</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3048,14 +3048,16 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
-      </c>
-      <c r="D157" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.8095138988831876</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>348 px x 442 px</t>
+          <t>354 px x 306 px</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3064,16 +3066,16 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.9810789139518461</v>
+        <v>0.5946338551524621</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>240 px x 120 px</t>
+          <t>396 px x 396 px</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3082,16 +3084,16 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D159" t="n">
-        <v>0.6043324980243541</v>
+        <v>-0.5944910198432918</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>126 px x 294 px</t>
+          <t>360 px x 360 px</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3100,16 +3102,16 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D160" t="n">
-        <v>0.7169924553074923</v>
+        <v>0.9453046848300437</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>454 px x 454 px</t>
+          <t>396 px x 484 px</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3118,16 +3120,16 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D161" t="n">
-        <v>1.498114058718078</v>
+        <v>-0.5684227252098543</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>320 px x 302 px</t>
+          <t>320 px x 385 px</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3136,16 +3138,16 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.5559725929565947</v>
+        <v>0.2357182339166525</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>120 px x 240 px</t>
+          <t>320 px x 302 px</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3154,16 +3156,16 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D163" t="n">
-        <v>-1.627212772898421</v>
+        <v>0.9773514823359014</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>396 px x 484 px</t>
+          <t>320 px x 320 px</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3172,16 +3174,16 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.7884101664197042</v>
+        <v>0.6630705388592734</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>312 px x 390 px</t>
+          <t>454 px x 454 px</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3190,14 +3192,16 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2</v>
-      </c>
-      <c r="D165" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1.379727296820575</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>396 px x 396 px</t>
+          <t>348 px x 442 px</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3206,16 +3210,16 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D166" t="n">
-        <v>-1.680339202039882</v>
+        <v>0.5635576650667438</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>390 px x 390 px</t>
+          <t>352 px x 430 px</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3224,16 +3228,14 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>9</v>
-      </c>
-      <c r="D167" t="n">
-        <v>0.08041653249887143</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>400 px x 400 px</t>
+          <t>194 px x 368 px</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3242,14 +3244,16 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2</v>
-      </c>
-      <c r="D168" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="D168" t="n">
+        <v>2.152061213110525</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>320 px x 320 px</t>
+          <t>208 px x 208 px</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3258,16 +3262,14 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>10</v>
-      </c>
-      <c r="D169" t="n">
-        <v>0.3670904936400634</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>128 px x 128 px</t>
+          <t>324 px x 394 px</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3276,14 +3278,14 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>160 px x 80 px</t>
+          <t>312 px x 390 px</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3294,38 +3296,312 @@
       <c r="C171" t="n">
         <v>2</v>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="n">
+        <v>-1.108481184863823</v>
+      </c>
     </row>
     <row r="172">
-      <c r="A172" t="n">
-        <v>0</v>
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>240 px x 120 px</t>
+        </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>8</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0.9159149901453512</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>192 px x 490 px</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>3</v>
+      </c>
+      <c r="D173" t="n">
+        <v>-1.03115149128752</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>128 px x 128 px</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>240 px x 280 px</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>2</v>
+      </c>
+      <c r="D175" t="n">
+        <v>-1.081133039155644</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>456 px x 280 px</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>120 px x 240 px</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>5</v>
+      </c>
+      <c r="D177" t="n">
+        <v>-1.462389985867876</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>390 px x 390 px</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>10</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0.7985135778235217</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>368 px x 448 px</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>3</v>
+      </c>
+      <c r="D179" t="n">
+        <v>-0.9964909107085158</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>400 x 400 px</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>2</v>
+      </c>
+      <c r="D180" t="n">
+        <v>-1.085830511782159</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>126 x 294</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>160x 80</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>160 px x 80 px</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>2</v>
+      </c>
+      <c r="D183" t="n">
+        <v>-1.298157658262833</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>152x486</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>240 * 240 pixeles</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>1</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
           <t>Con pantalla táctil</t>
         </is>
       </c>
-      <c r="C172" t="n">
-        <v>59</v>
-      </c>
-      <c r="D172" t="n">
-        <v>-0.7071067811865475</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
+      <c r="C186" t="n">
+        <v>323</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0.7071067811865476</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>0</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Con pantalla táctil</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>70</v>
+      </c>
+      <c r="D187" t="n">
+        <v>-0.7071067811865476</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
         <v>1</v>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Con pantalla táctil</t>
-        </is>
-      </c>
-      <c r="C173" t="n">
-        <v>290</v>
-      </c>
-      <c r="D173" t="n">
-        <v>0.7071067811865476</v>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Es resistente al agua</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>569</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0.7071067811865474</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>0</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Es resistente al agua</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>95</v>
+      </c>
+      <c r="D189" t="n">
+        <v>-0.7071067811865478</v>
       </c>
     </row>
   </sheetData>

--- a/data/modelling/atribucion/smartband/df_attr_values_sent.xlsx
+++ b/data/modelling/atribucion/smartband/df_attr_values_sent.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D189"/>
+  <dimension ref="A1:D127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5135</v>
+        <v>10660.5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -460,15 +460,15 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1400296842341354</v>
+        <v>0.9749132717546283</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4099</v>
+        <v>5012.5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -476,15 +476,15 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1973745530503195</v>
+        <v>0.2142225750992265</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>14699</v>
+        <v>3385</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -492,15 +492,15 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.095526884265465</v>
+        <v>-0.6839576305481861</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7735</v>
+        <v>6455</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -508,15 +508,15 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>177</v>
+        <v>103</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6349593455072242</v>
+        <v>0.8103004433269447</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2167.5</v>
+        <v>17689.5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -524,15 +524,15 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.182487695691351</v>
+        <v>-1.864016435156873</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9327.5</v>
+        <v>1495</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -540,15 +540,15 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="D7" t="n">
-        <v>1.754890909609559</v>
+        <v>-0.08228674317792115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6298.5</v>
+        <v>7995</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -556,48 +556,52 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.012350484243395</v>
+        <v>0.6308245187021843</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>1119.5</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>precio</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3001503667594382</v>
+        <v>0.9517035507663677</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>3139.5</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Imilab</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>precio</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>43</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8632609385584101</v>
+        <v>1.252247293542846</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -606,16 +610,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>1.063104293949428</v>
+        <v>-1.849361771535483</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Imilab</t>
+          <t>Microwear</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -624,16 +628,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D12" t="n">
-        <v>1.102815984644837</v>
+        <v>-0.1002609923018855</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Amazfit</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -642,16 +646,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.776409596485399</v>
+        <v>0.945788347864142</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Amazfit</t>
+          <t>Smart Bracelet D20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -660,10 +664,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7966452242808992</v>
+        <v>-0.8367473529091313</v>
       </c>
     </row>
     <row r="15">
@@ -678,16 +682,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>1.08012981954892</v>
+        <v>1.087545868237482</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>DT NO.1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -696,16 +700,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3535735873121599</v>
+        <v>0.7648467856777675</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Smart Bracelet D20</t>
+          <t>Colmi</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -714,16 +718,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.055167278614703</v>
+        <v>0.7118331041298458</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Colmi</t>
+          <t>Nictom</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -732,16 +736,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6548279141237334</v>
+        <v>0.7906731210711891</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Honor</t>
+          <t>Mia</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -750,16 +754,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D19" t="n">
-        <v>1.484492854287341</v>
+        <v>1.054828556990148</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Microwear</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -768,16 +772,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1760685720910358</v>
+        <v>-1.595486353972035</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DT NO.1</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -786,16 +790,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7550029798336428</v>
+        <v>0.2468780524436013</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Noga</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -804,16 +808,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.353720378570089</v>
+        <v>-1.215472717487393</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>You</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -822,16 +826,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D23" t="n">
-        <v>1.473592290914306</v>
+        <v>0.7879083390990954</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Kospet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -840,16 +844,14 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>12</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-0.4968093041002776</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nictom</t>
+          <t>BlueStar</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -858,16 +860,14 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>75</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.3178217137152378</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Shirajo</t>
+          <t>Genérica</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -876,16 +876,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.01681791354602649</v>
+        <v>-0.3242770225846527</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SmartWatches</t>
+          <t>Shirajo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4794953211555674</v>
+        <v>0.3873660017960897</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Belmotec</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -912,16 +912,14 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>30</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.6691890834708132</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Suono</t>
+          <t>Kingwear</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -930,16 +928,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.043197855406991</v>
+        <v>1.233004341139398</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gadnic</t>
+          <t>SmartWatches</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -948,14 +946,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.4423179075751435</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Y9</t>
+          <t>PSP_BAND</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>126</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>1.45151089479102</v>
+        <v>-0.8764017825110595</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Gadnic</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PSP_BAND</t>
+          <t>Goufit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -998,16 +998,14 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
-      </c>
-      <c r="D33" t="n">
-        <v>-1.096678076763771</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kingwear</t>
+          <t>Netmak</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1016,16 +1014,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="D34" t="n">
-        <v>1.187173537787878</v>
+        <v>0.1863221046788525</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Genérica</t>
+          <t>Honor</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1034,16 +1032,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4340865515426019</v>
+        <v>-0.1354869303465099</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mia</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1052,16 +1050,14 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>19</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.3610673833418932</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kospet</t>
+          <t>Noga</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1070,16 +1066,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9373469967856028</v>
+        <v>-0.006913272737370284</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ruffo</t>
+          <t>Daikon</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1088,16 +1084,14 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-1.548711301660805</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Belmotec</t>
+          <t>Mibro</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1106,16 +1100,14 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>24</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.8255162515443665</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Libercam</t>
+          <t>Daza</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1124,16 +1116,14 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-1.649054418704722</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Gen</t>
+          <t>HiFuture</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1149,7 +1139,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Integra</t>
+          <t>Ruffo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1158,16 +1148,14 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>18</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.7177375010306692</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Goufit</t>
+          <t>HDT8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1176,16 +1164,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.517575608611315</v>
+        <v>-1.764240533968805</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>JAZAK</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1194,14 +1182,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-1.077169574085919</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Geko</t>
+          <t>Doogee</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1210,16 +1200,14 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
-      </c>
-      <c r="D45" t="n">
-        <v>-0.815465660547558</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Netmak</t>
+          <t>Level Up</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1228,16 +1216,14 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37</v>
-      </c>
-      <c r="D46" t="n">
-        <v>1.203176706140756</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Aiwa Time</t>
+          <t>Rohs</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1246,14 +1232,14 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>y68 smart Bracelet</t>
+          <t>ISANFIT</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1262,14 +1248,14 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Veryfit</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1278,16 +1264,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.9073858843636076</v>
+        <v>-1.541613633267272</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Smartwatches</t>
+          <t>Phull</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1296,16 +1282,14 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
-      </c>
-      <c r="D50" t="n">
-        <v>-1.02364313035354</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ISANFIT</t>
+          <t>Haxly</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1321,7 +1305,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Daza</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1337,7 +1321,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HDT8</t>
+          <t>Soul</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1346,14 +1330,14 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Skmei</t>
+          <t>Integra</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1362,14 +1346,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.023429372904421</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Solana</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1385,7 +1371,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Smart Bracalet</t>
+          <t>Uprint</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1394,14 +1380,14 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SmartBand</t>
+          <t>WICKPRO</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1417,7 +1403,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>mentedigital</t>
+          <t>ONCELULAR2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1433,7 +1419,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>X-View</t>
+          <t>T-Go</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1442,14 +1428,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-0.5432608102088712</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Bazar</t>
+          <t>IWO</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1458,14 +1446,14 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Soul</t>
+          <t>JAZAK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1474,14 +1462,14 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Veryfit</t>
+          <t>LCS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1490,14 +1478,14 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tecnocenter</t>
+          <t>Tressa</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1506,16 +1494,14 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>18</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0.6917717203323291</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DX</t>
+          <t>WickPro</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1524,16 +1510,14 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
-      </c>
-      <c r="D64" t="n">
-        <v>-1.176768966351714</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>T-Go</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1542,16 +1526,14 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
-      </c>
-      <c r="D65" t="n">
-        <v>-0.8120168682791865</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Otras Marcas</t>
+          <t>Suono</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1560,14 +1542,14 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Y68</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1576,14 +1558,14 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>sw68k</t>
+          <t>Kanji</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1592,16 +1574,14 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
-      </c>
-      <c r="D68" t="n">
-        <v>-1.344883772069807</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AIWA TIME</t>
+          <t>Solana</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1617,7 +1597,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BlueStar</t>
+          <t>X8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1633,7 +1613,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mibro</t>
+          <t>LEZAYA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1649,7 +1629,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FULL-TIME MANIA</t>
+          <t>Reloj Smartband M6</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1665,7 +1645,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HiFuture</t>
+          <t>SMART WATCH BRACELET</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1679,400 +1659,388 @@
       <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Targa</t>
-        </is>
+      <c r="A74" t="n">
+        <v>185</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" t="inlineStr"/>
+        <v>122</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.648400912652189</v>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
+      <c r="A75" t="n">
+        <v>142</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-0.01269752516545522</v>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Kieslect</t>
-        </is>
+      <c r="A76" t="n">
+        <v>375</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.937706356084413</v>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>IWO</t>
-        </is>
+      <c r="A77" t="n">
+        <v>296</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-0.2080965616666333</v>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>aiwa time</t>
-        </is>
+      <c r="A78" t="n">
+        <v>240</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" t="inlineStr"/>
+        <v>117</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.4845575277437915</v>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Mistral</t>
-        </is>
+      <c r="A79" t="n">
+        <v>82.5</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-1.849870709648305</v>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Aiwa time</t>
-        </is>
+      <c r="A80" t="n">
+        <v>120</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Duración de la batería</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-0.4205130395284329</v>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Doogee</t>
-        </is>
+      <c r="A81" t="n">
+        <v>276</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Duración de la batería</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" t="inlineStr"/>
+        <v>143</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.8767484085800109</v>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Kolke</t>
-        </is>
+      <c r="A82" t="n">
+        <v>468</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Duración de la batería</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" t="inlineStr"/>
+        <v>115</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.7594058989020102</v>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
+      <c r="A83" t="n">
+        <v>29</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Duración de la batería</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-1.215641267953588</v>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Sweet</t>
-        </is>
+      <c r="A84" t="n">
+        <v>40.64</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.9316692403793179</v>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>X8</t>
-        </is>
+      <c r="A85" t="n">
+        <v>28.829</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.158016086403899</v>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Rohs</t>
-        </is>
+      <c r="A86" t="n">
+        <v>33.756</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="D86" t="n">
+        <v>-0.1776875537143231</v>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>TPU/Aleación de aluminio</t>
-        </is>
+      <c r="A87" t="n">
+        <v>43.22499999999999</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C87" t="n">
+        <v>16</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-0.7198358953547285</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>37.211</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>70</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1.234111465714372</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>52.479</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>5</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>19.208</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
         <v>13</v>
       </c>
-      <c r="D87" t="n">
-        <v>-0.4109908462209463</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Elastómero termoplástico/Aleación de aluminio</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Material de la malla</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>16</v>
-      </c>
-      <c r="D88" t="n">
-        <v>-0.8786463318116875</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Silicona</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Material de la malla</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>367</v>
-      </c>
-      <c r="D89" t="n">
-        <v>0.8685263568095842</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>TPU</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Material de la malla</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>34</v>
-      </c>
       <c r="D90" t="n">
-        <v>-0.4955484184498232</v>
+        <v>-1.426273343428538</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Fluoroelastómero</t>
+          <t>AMOLED</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="D91" t="n">
-        <v>1.115803373946772</v>
+        <v>1.13044399796474</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Caucho de silicona</t>
+          <t>LCD TFT</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.5877212548313471</v>
+        <v>1.02584432162282</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Plástico</t>
+          <t>LCD IPS</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.9162835826786969</v>
+        <v>-0.4363898758620342</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cuero</t>
+          <t>LTPS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>11</v>
-      </c>
-      <c r="D94" t="n">
-        <v>-0.526090141715073</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Caucho</t>
+          <t>SAMOLED</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
-      </c>
-      <c r="D95" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-0.8481521217936039</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Acero inoxidable</t>
+          <t>LTPO OLED</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>44</v>
-      </c>
-      <c r="D96" t="n">
-        <v>1.830950844951218</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1ra Metal - 2da Silicona</t>
+          <t>LCD MIP</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -2083,12 +2051,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TPU 24 mm</t>
+          <t>Táctil</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2099,71 +2067,73 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Acero inoxidable/Silicona</t>
+          <t>IPS</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>6</v>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="n">
+        <v>-0.8717463219319229</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Elastómero termoplástico</t>
+          <t>LCD</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cuero Genuino</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1ra Cuero/TPU - 2da Silicona negra</t>
+          <t>TFT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Rosa / negra</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2172,14 +2142,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>7</v>
-      </c>
-      <c r="D103" t="inlineStr"/>
+        <v>256</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.8423638911061223</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Acero inoxidable - silicona</t>
+          <t>TPU/Aleación de aluminio</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2188,14 +2160,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>8</v>
-      </c>
-      <c r="D104" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-0.4324989293697984</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Elastómero termoplástico/Aleación de aluminio</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2204,14 +2178,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-0.8627184014280733</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Resina</t>
+          <t>TPU</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2220,14 +2196,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="D106" t="n">
+        <v>-0.3311637131353162</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Silicona, Metal, Cuero</t>
+          <t>Caucho de silicona</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2236,14 +2214,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-0.5812035884071254</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Nailon</t>
+          <t>Fluoroelastómero</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2252,1356 +2232,320 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.8694400356150865</v>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" t="n">
-        <v>0.02</v>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Cuero</t>
+        </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>196</v>
+        <v>11</v>
       </c>
       <c r="D109" t="n">
-        <v>0.8767838511050374</v>
+        <v>-0.4543016971181653</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="n">
-        <v>0.06</v>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Acero inoxidable</t>
+        </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D110" t="n">
-        <v>-1.338508766074603</v>
+        <v>1.97470339687913</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="n">
-        <v>0.04</v>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Caucho</t>
+        </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>99</v>
-      </c>
-      <c r="D111" t="n">
-        <v>0.6389368459429643</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="n">
-        <v>0.05</v>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Plástico</t>
+        </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.1772119309733993</v>
+        <v>-1.024620994141859</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="n">
-        <v>0</v>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="n">
-        <v>112.5</v>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Acero inoxidable/Silicona</t>
+        </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>94</v>
-      </c>
-      <c r="D114" t="n">
-        <v>1.119757970747649</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="n">
-        <v>360</v>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1ra Cuero/TPU - 2da Silicona negra</t>
+        </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>75</v>
-      </c>
-      <c r="D115" t="n">
-        <v>-0.3954217722000818</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="n">
-        <v>251</v>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1ra Metal - 2da Silicona</t>
+        </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>53</v>
-      </c>
-      <c r="D116" t="n">
-        <v>-0.6826895475654101</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="n">
-        <v>147</v>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Cuero Genuino</t>
+        </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>25</v>
-      </c>
-      <c r="D117" t="n">
-        <v>-0.7211657859987519</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" t="n">
-        <v>215</v>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Rosa / negra</t>
+        </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>156</v>
-      </c>
-      <c r="D118" t="n">
-        <v>0.374409966386717</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" t="n">
-        <v>305</v>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>58</v>
-      </c>
-      <c r="D119" t="n">
-        <v>-0.2449593766470788</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>175</v>
+        <v>1</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
+          <t>Es resistente al agua</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>120</v>
+        <v>416</v>
       </c>
       <c r="D120" t="n">
-        <v>1.733143146896229</v>
+        <v>0.707106781186548</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
+          <t>Es resistente al agua</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D121" t="n">
-        <v>-1.183074601619272</v>
+        <v>-0.707106781186547</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>288</v>
+        <v>0.0131</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="D122" t="n">
-        <v>1.377902800004959</v>
+        <v>1.181963330339621</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>468</v>
+        <v>0.0535</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>132</v>
+        <v>64</v>
       </c>
       <c r="D123" t="n">
-        <v>0.550924154952558</v>
+        <v>-1.005855113373139</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>29</v>
+        <v>0.0399</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.9367332787406575</v>
+        <v>-0.6245758343210811</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>192</v>
+        <v>0.0275</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="D125" t="n">
-        <v>0.4465510650442625</v>
+        <v>0.4484676173545947</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
+          <t>Con pantalla táctil</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.1336005875898513</v>
+        <v>-0.7071067811865478</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
+          <t>Con pantalla táctil</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>30</v>
+        <v>270</v>
       </c>
       <c r="D127" t="n">
-        <v>-1.30504415367127</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>40.31</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>71</v>
-      </c>
-      <c r="D128" t="n">
-        <v>0.8367542873962608</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>28.46</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>37</v>
-      </c>
-      <c r="D129" t="n">
-        <v>-0.6957555653817187</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>104</v>
-      </c>
-      <c r="D130" t="n">
-        <v>-0.6440050888914576</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>44.26</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>29</v>
-      </c>
-      <c r="D131" t="n">
-        <v>0.8711759238939062</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>36.36</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>83</v>
-      </c>
-      <c r="D132" t="n">
-        <v>0.9504419949783185</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>33</v>
-      </c>
-      <c r="D133" t="n">
-        <v>-1.31861155199531</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>64.03</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>1</v>
-      </c>
-      <c r="D134" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>6</v>
-      </c>
-      <c r="D135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>60.08</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>AMOLED</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>146</v>
-      </c>
-      <c r="D138" t="n">
-        <v>1.500709363758677</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>LCD TFT</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>81</v>
-      </c>
-      <c r="D139" t="n">
-        <v>1.118273604732085</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>SAMOLED</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>12</v>
-      </c>
-      <c r="D140" t="n">
-        <v>-0.7360139922902258</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>LTPO OLED</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>8</v>
-      </c>
-      <c r="D141" t="n">
-        <v>-0.220120477027843</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>LCD IPS</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>29</v>
-      </c>
-      <c r="D142" t="n">
-        <v>0.2282393860541106</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>LTPS</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>2</v>
-      </c>
-      <c r="D143" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>LCD MIP</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>0</v>
-      </c>
-      <c r="D144" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>2</v>
-      </c>
-      <c r="D145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Táctil</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>0</v>
-      </c>
-      <c r="D146" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>LCD</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>6</v>
-      </c>
-      <c r="D147" t="n">
-        <v>-1.128527571745116</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>IPS</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>6</v>
-      </c>
-      <c r="D148" t="n">
-        <v>-0.7625603134816871</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>TFT IPS</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="C149" t="n">
-        <v>2</v>
-      </c>
-      <c r="D149" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>TFT</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="C150" t="n">
-        <v>4</v>
-      </c>
-      <c r="D150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Digital</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>0</v>
-      </c>
-      <c r="D151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>TFT LCD</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>0</v>
-      </c>
-      <c r="D152" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>152 px x 486 px</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
-        <v>19</v>
-      </c>
-      <c r="D153" t="n">
-        <v>0.5357927150182237</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>126 px x 29 px</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
-        <v>13</v>
-      </c>
-      <c r="D154" t="n">
-        <v>-0.3035583087429916</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>240 px x 240 px</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
-        <v>56</v>
-      </c>
-      <c r="D155" t="n">
-        <v>-0.1574804054114195</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>320 px x 360 px</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>6</v>
-      </c>
-      <c r="D156" t="n">
-        <v>-0.8835729108265354</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>126 px x 294 px</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
-        <v>14</v>
-      </c>
-      <c r="D157" t="n">
-        <v>0.8095138988831876</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>354 px x 306 px</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
-        <v>16</v>
-      </c>
-      <c r="D158" t="n">
-        <v>0.5946338551524621</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>396 px x 396 px</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
-        <v>12</v>
-      </c>
-      <c r="D159" t="n">
-        <v>-0.5944910198432918</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>360 px x 360 px</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
-        <v>11</v>
-      </c>
-      <c r="D160" t="n">
-        <v>0.9453046848300437</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>396 px x 484 px</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C161" t="n">
-        <v>3</v>
-      </c>
-      <c r="D161" t="n">
-        <v>-0.5684227252098543</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>320 px x 385 px</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C162" t="n">
-        <v>11</v>
-      </c>
-      <c r="D162" t="n">
-        <v>0.2357182339166525</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>320 px x 302 px</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
-        <v>17</v>
-      </c>
-      <c r="D163" t="n">
-        <v>0.9773514823359014</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>320 px x 320 px</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C164" t="n">
-        <v>10</v>
-      </c>
-      <c r="D164" t="n">
-        <v>0.6630705388592734</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>454 px x 454 px</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
-        <v>17</v>
-      </c>
-      <c r="D165" t="n">
-        <v>1.379727296820575</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>348 px x 442 px</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C166" t="n">
-        <v>18</v>
-      </c>
-      <c r="D166" t="n">
-        <v>0.5635576650667438</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>352 px x 430 px</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C167" t="n">
-        <v>1</v>
-      </c>
-      <c r="D167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>194 px x 368 px</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>12</v>
-      </c>
-      <c r="D168" t="n">
-        <v>2.152061213110525</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>208 px x 208 px</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C169" t="n">
-        <v>0</v>
-      </c>
-      <c r="D169" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>324 px x 394 px</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C170" t="n">
-        <v>1</v>
-      </c>
-      <c r="D170" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>312 px x 390 px</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C171" t="n">
-        <v>2</v>
-      </c>
-      <c r="D171" t="n">
-        <v>-1.108481184863823</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>240 px x 120 px</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C172" t="n">
-        <v>8</v>
-      </c>
-      <c r="D172" t="n">
-        <v>0.9159149901453512</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>192 px x 490 px</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C173" t="n">
-        <v>3</v>
-      </c>
-      <c r="D173" t="n">
-        <v>-1.03115149128752</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>128 px x 128 px</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C174" t="n">
-        <v>0</v>
-      </c>
-      <c r="D174" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>240 px x 280 px</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C175" t="n">
-        <v>2</v>
-      </c>
-      <c r="D175" t="n">
-        <v>-1.081133039155644</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>456 px x 280 px</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C176" t="n">
-        <v>1</v>
-      </c>
-      <c r="D176" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>120 px x 240 px</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C177" t="n">
-        <v>5</v>
-      </c>
-      <c r="D177" t="n">
-        <v>-1.462389985867876</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>390 px x 390 px</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C178" t="n">
-        <v>10</v>
-      </c>
-      <c r="D178" t="n">
-        <v>0.7985135778235217</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>368 px x 448 px</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C179" t="n">
-        <v>3</v>
-      </c>
-      <c r="D179" t="n">
-        <v>-0.9964909107085158</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>400 x 400 px</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C180" t="n">
-        <v>2</v>
-      </c>
-      <c r="D180" t="n">
-        <v>-1.085830511782159</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>126 x 294</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C181" t="n">
-        <v>0</v>
-      </c>
-      <c r="D181" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>160x 80</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C182" t="n">
-        <v>1</v>
-      </c>
-      <c r="D182" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>160 px x 80 px</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C183" t="n">
-        <v>2</v>
-      </c>
-      <c r="D183" t="n">
-        <v>-1.298157658262833</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>152x486</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C184" t="n">
-        <v>0</v>
-      </c>
-      <c r="D184" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>240 * 240 pixeles</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="C185" t="n">
-        <v>0</v>
-      </c>
-      <c r="D185" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>1</v>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Con pantalla táctil</t>
-        </is>
-      </c>
-      <c r="C186" t="n">
-        <v>323</v>
-      </c>
-      <c r="D186" t="n">
-        <v>0.7071067811865476</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>0</v>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Con pantalla táctil</t>
-        </is>
-      </c>
-      <c r="C187" t="n">
-        <v>70</v>
-      </c>
-      <c r="D187" t="n">
-        <v>-0.7071067811865476</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>1</v>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Es resistente al agua</t>
-        </is>
-      </c>
-      <c r="C188" t="n">
-        <v>569</v>
-      </c>
-      <c r="D188" t="n">
         <v>0.7071067811865474</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>0</v>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Es resistente al agua</t>
-        </is>
-      </c>
-      <c r="C189" t="n">
-        <v>95</v>
-      </c>
-      <c r="D189" t="n">
-        <v>-0.7071067811865478</v>
       </c>
     </row>
   </sheetData>

--- a/data/modelling/atribucion/smartband/df_attr_values_sent.xlsx
+++ b/data/modelling/atribucion/smartband/df_attr_values_sent.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D127"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
         <v>82</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9749132717546283</v>
+        <v>1.055855577370933</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2142225750992265</v>
+        <v>0.2631702585882758</v>
       </c>
     </row>
     <row r="4">
@@ -495,12 +495,12 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6839576305481861</v>
+        <v>-0.6234949305327382</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6455</v>
+        <v>6444.5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
         <v>103</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8103004433269447</v>
+        <v>0.884319034583219</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.864016435156873</v>
+        <v>-1.868746293813093</v>
       </c>
     </row>
     <row r="7">
@@ -543,12 +543,12 @@
         <v>128</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.08228674317792115</v>
+        <v>-0.09134947909007532</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7995</v>
+        <v>7930</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6308245187021843</v>
+        <v>0.3802458328934776</v>
       </c>
     </row>
     <row r="9">
@@ -577,7 +577,7 @@
         <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9517035507663677</v>
+        <v>0.899121363459184</v>
       </c>
     </row>
     <row r="10">
@@ -595,7 +595,7 @@
         <v>43</v>
       </c>
       <c r="D10" t="n">
-        <v>1.252247293542846</v>
+        <v>1.211422833854932</v>
       </c>
     </row>
     <row r="11">
@@ -610,10 +610,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.849361771535483</v>
+        <v>-2.013367531221349</v>
       </c>
     </row>
     <row r="12">
@@ -631,7 +631,7 @@
         <v>31</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1002609923018855</v>
+        <v>-0.1939978385867257</v>
       </c>
     </row>
     <row r="13">
@@ -649,7 +649,7 @@
         <v>92</v>
       </c>
       <c r="D13" t="n">
-        <v>0.945788347864142</v>
+        <v>0.8929748307109314</v>
       </c>
     </row>
     <row r="14">
@@ -667,7 +667,7 @@
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8367473529091313</v>
+        <v>-0.9875483880610821</v>
       </c>
     </row>
     <row r="15">
@@ -685,7 +685,7 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>1.087545868237482</v>
+        <v>1.040277639773483</v>
       </c>
     </row>
     <row r="16">
@@ -703,7 +703,7 @@
         <v>28</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7648467856777675</v>
+        <v>0.7049543608315747</v>
       </c>
     </row>
     <row r="17">
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7118331041298458</v>
+        <v>0.9450687180310372</v>
       </c>
     </row>
     <row r="18">
@@ -739,7 +739,7 @@
         <v>51</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7906731210711891</v>
+        <v>0.7317908370472577</v>
       </c>
     </row>
     <row r="19">
@@ -757,13 +757,13 @@
         <v>20</v>
       </c>
       <c r="D19" t="n">
-        <v>1.054828556990148</v>
+        <v>0.9317145594387042</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.595486353972035</v>
+        <v>0.1119379998726587</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>You</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2468780524436013</v>
+        <v>0.7289180156124762</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Kospet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -808,16 +808,14 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-1.215472717487393</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>BlueStar</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -826,16 +824,14 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>31</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.7879083390990954</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kospet</t>
+          <t>Genérica</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -844,14 +840,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.467577057749842</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BlueStar</t>
+          <t>Shirajo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -860,14 +858,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.1181342791259239</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Genérica</t>
+          <t>Belmotec</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -876,16 +876,14 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-0.3242770225846527</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Shirajo</t>
+          <t>Kingwear</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -894,16 +892,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3873660017960897</v>
+        <v>1.191426755195605</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Belmotec</t>
+          <t>SmartWatches</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -912,14 +910,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.3698076789587996</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kingwear</t>
+          <t>PSP_BAND</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -928,16 +928,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>1.233004341139398</v>
+        <v>-1.027783232399406</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SmartWatches</t>
+          <t>Gadnic</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -946,16 +946,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.4423179075751435</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PSP_BAND</t>
+          <t>Goufit</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -964,16 +962,14 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
-      </c>
-      <c r="D31" t="n">
-        <v>-0.8764017825110595</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gadnic</t>
+          <t>Netmak</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -982,14 +978,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.05049564068011295</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Goufit</t>
+          <t>Honor</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -998,14 +996,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.276023949561949</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Netmak</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1014,16 +1014,14 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.1863221046788525</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Honor</t>
+          <t>Noga</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1032,16 +1030,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1354869303465099</v>
+        <v>-0.3089983889080233</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Daikon</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1050,14 +1048,14 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Noga</t>
+          <t>Mibro</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1066,16 +1064,14 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>19</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-0.006913272737370284</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Daikon</t>
+          <t>Daza</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1084,14 +1080,14 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mibro</t>
+          <t>HiFuture</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1100,14 +1096,14 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Daza</t>
+          <t>Ruffo</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1116,14 +1112,14 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HiFuture</t>
+          <t>HDT8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1132,14 +1128,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-1.928617288657353</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ruffo</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1148,14 +1146,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-1.231489629931741</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HDT8</t>
+          <t>Doogee</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1164,16 +1164,14 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
-      </c>
-      <c r="D43" t="n">
-        <v>-1.764240533968805</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Level Up</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1182,16 +1180,14 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
-      </c>
-      <c r="D44" t="n">
-        <v>-1.077169574085919</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Doogee</t>
+          <t>Rohs</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1207,7 +1203,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Level Up</t>
+          <t>ISANFIT</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1223,7 +1219,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Rohs</t>
+          <t>Veryfit</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1232,14 +1228,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-1.70273178450078</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ISANFIT</t>
+          <t>Phull</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1255,7 +1253,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Veryfit</t>
+          <t>Haxly</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1264,16 +1262,14 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
-      </c>
-      <c r="D49" t="n">
-        <v>-1.541613633267272</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Phull</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1289,7 +1285,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Haxly</t>
+          <t>Soul</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1305,7 +1301,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>Integra</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1314,14 +1310,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.8998556324164519</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Soul</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1337,7 +1335,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Integra</t>
+          <t>Uprint</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1346,16 +1344,14 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>17</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1.023429372904421</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>WICKPRO</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1371,7 +1367,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Uprint</t>
+          <t>ONCELULAR2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1387,7 +1383,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WICKPRO</t>
+          <t>T-Go</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1396,14 +1392,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-0.6897660554308787</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ONCELULAR2</t>
+          <t>IWO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1419,7 +1417,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>T-Go</t>
+          <t>JAZAK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1428,16 +1426,14 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
-      </c>
-      <c r="D59" t="n">
-        <v>-0.5432608102088712</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IWO</t>
+          <t>LCS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1446,14 +1442,14 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>JAZAK</t>
+          <t>Tressa</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1462,14 +1458,14 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LCS</t>
+          <t>WickPro</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1478,14 +1474,14 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tressa</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1501,7 +1497,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WickPro</t>
+          <t>Suono</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1517,7 +1513,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1533,7 +1529,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Suono</t>
+          <t>Kanji</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1549,7 +1545,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>Solana</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1565,7 +1561,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kanji</t>
+          <t>X8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1581,7 +1577,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Solana</t>
+          <t>LEZAYA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1597,7 +1593,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>X8</t>
+          <t>Reloj Smartband M6</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1613,7 +1609,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LEZAYA</t>
+          <t>SMART WATCH BRACELET</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1627,40 +1623,40 @@
       <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Reloj Smartband M6</t>
-        </is>
+      <c r="A72" t="n">
+        <v>185</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" t="inlineStr"/>
+        <v>119</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.5128526212504075</v>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>SMART WATCH BRACELET</t>
-        </is>
+      <c r="A73" t="n">
+        <v>142</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-0.04779369282183864</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>185</v>
+        <v>375</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -1668,15 +1664,15 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="D74" t="n">
-        <v>0.648400912652189</v>
+        <v>0.7393994135284503</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>142</v>
+        <v>296</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -1684,15 +1680,15 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.01269752516545522</v>
+        <v>-0.2738141743229234</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -1700,15 +1696,15 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D76" t="n">
-        <v>0.937706356084413</v>
+        <v>0.8911370887423397</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>296</v>
+        <v>82.5</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -1716,47 +1712,47 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.2080965616666333</v>
+        <v>-1.821781256376436</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>240</v>
+        <v>168</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
+          <t>Duración de la batería</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="D78" t="n">
-        <v>0.4845575277437915</v>
+        <v>0.5595477917045737</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>82.5</v>
+        <v>288</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
+          <t>Duración de la batería</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.849870709648305</v>
+        <v>0.2719995332055359</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120</v>
+        <v>468</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -1764,15 +1760,15 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.4205130395284329</v>
+        <v>0.6489298281825794</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>276</v>
+        <v>56</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -1780,47 +1776,47 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>143</v>
+        <v>25</v>
       </c>
       <c r="D81" t="n">
-        <v>0.8767484085800109</v>
+        <v>-1.480477153092689</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>468</v>
+        <v>40.64</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="D82" t="n">
-        <v>0.7594058989020102</v>
+        <v>0.8238185741505839</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>29</v>
+        <v>30.099</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Duración de la batería</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="D83" t="n">
-        <v>-1.215641267953588</v>
+        <v>0.4358885755785805</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>40.64</v>
+        <v>43.22499999999999</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -1828,15 +1824,15 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="D84" t="n">
-        <v>0.9316692403793179</v>
+        <v>-0.6770457472582471</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>28.829</v>
+        <v>34.163</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -1844,15 +1840,15 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D85" t="n">
-        <v>0.158016086403899</v>
+        <v>-0.484824784060277</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>33.756</v>
+        <v>37.33799999999999</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -1860,15 +1856,15 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.1776875537143231</v>
+        <v>1.261251925820264</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>43.22499999999999</v>
+        <v>19.335</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -1876,15 +1872,15 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.7198358953547285</v>
+        <v>-1.359088544230904</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>37.211</v>
+        <v>52.479</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -1892,46 +1888,50 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>70</v>
-      </c>
-      <c r="D88" t="n">
-        <v>1.234111465714372</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="n">
-        <v>52.479</v>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AMOLED</t>
+        </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
-      </c>
-      <c r="D89" t="inlineStr"/>
+        <v>123</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.8989412771858279</v>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
-        <v>19.208</v>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>LCD TFT</t>
+        </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="D90" t="n">
-        <v>-1.426273343428538</v>
+        <v>0.8175982199607241</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AMOLED</t>
+          <t>LCD IPS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1940,16 +1940,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>127</v>
+        <v>19</v>
       </c>
       <c r="D91" t="n">
-        <v>1.13044399796474</v>
+        <v>-0.6998655058010271</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LCD TFT</t>
+          <t>LTPS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1958,16 +1958,14 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>77</v>
-      </c>
-      <c r="D92" t="n">
-        <v>1.02584432162282</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LCD IPS</t>
+          <t>SAMOLED</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1976,16 +1974,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.4363898758620342</v>
+        <v>-1.016673991345525</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LTPS</t>
+          <t>Táctil</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1994,14 +1992,14 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SAMOLED</t>
+          <t>IPS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2010,16 +2008,14 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>12</v>
-      </c>
-      <c r="D95" t="n">
-        <v>-0.8481521217936039</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>LTPO OLED</t>
+          <t>LCD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2028,14 +2024,14 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LCD MIP</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2051,7 +2047,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Táctil</t>
+          <t>TFT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2060,80 +2056,86 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IPS</t>
+          <t>Silicona</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>244</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.8717463219319229</v>
+        <v>1.234950459141323</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LCD</t>
+          <t>TPU/Aleación de aluminio</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>5</v>
-      </c>
-      <c r="D100" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-0.1232981474784827</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>Elastómero termoplástico/Aleación de aluminio</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-0.6520726408526637</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TFT</t>
+          <t>TPU</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Tipo de pantalla</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
-      </c>
-      <c r="D102" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.001251172932257644</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Silicona</t>
+          <t>Caucho de silicona</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2142,16 +2144,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>256</v>
+        <v>17</v>
       </c>
       <c r="D103" t="n">
-        <v>0.8423638911061223</v>
+        <v>-0.3060680595009452</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TPU/Aleación de aluminio</t>
+          <t>Fluoroelastómero</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2160,16 +2162,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.4324989293697984</v>
+        <v>0.4858723588604913</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Elastómero termoplástico/Aleación de aluminio</t>
+          <t>Cuero</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2181,13 +2183,13 @@
         <v>11</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.8627184014280733</v>
+        <v>-0.1500954042005175</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TPU</t>
+          <t>Acero inoxidable</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2196,16 +2198,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.3311637131353162</v>
+        <v>2.266885902735144</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Caucho de silicona</t>
+          <t>Caucho</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2214,16 +2216,14 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>17</v>
-      </c>
-      <c r="D107" t="n">
-        <v>-0.5812035884071254</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Fluoroelastómero</t>
+          <t>Plástico</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2232,16 +2232,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D108" t="n">
-        <v>0.8694400356150865</v>
+        <v>-0.8510639781586837</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Cuero</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2250,16 +2250,14 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>11</v>
-      </c>
-      <c r="D109" t="n">
-        <v>-0.4543016971181653</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Acero inoxidable</t>
+          <t>Acero inoxidable/Silicona</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2268,16 +2266,14 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>43</v>
-      </c>
-      <c r="D110" t="n">
-        <v>1.97470339687913</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Caucho</t>
+          <t>1ra Cuero/TPU - 2da Silicona negra</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2293,7 +2289,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Plástico</t>
+          <t>1ra Metal - 2da Silicona</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2302,16 +2298,14 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>13</v>
-      </c>
-      <c r="D112" t="n">
-        <v>-1.024620994141859</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Cuero Genuino</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2320,14 +2314,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-0.9850195854167664</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Acero inoxidable/Silicona</t>
+          <t>Rosa / negra</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2336,14 +2332,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>6</v>
-      </c>
-      <c r="D114" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-0.9213420780611582</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1ra Cuero/TPU - 2da Silicona negra</t>
+          <t>Resina</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2357,195 +2355,131 @@
       <c r="D115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>1ra Metal - 2da Silicona</t>
-        </is>
+      <c r="A116" t="n">
+        <v>1</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Es resistente al agua</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" t="inlineStr"/>
+        <v>391</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.7071067811865475</v>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Cuero Genuino</t>
-        </is>
+      <c r="A117" t="n">
+        <v>0</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Es resistente al agua</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>7</v>
-      </c>
-      <c r="D117" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-0.7071067811865475</v>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Rosa / negra</t>
-        </is>
+      <c r="A118" t="n">
+        <v>0.0126</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>7</v>
-      </c>
-      <c r="D118" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.1925106771872289</v>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Resina</t>
-        </is>
+      <c r="A119" t="n">
+        <v>0.054</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-0.6218721972333383</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1</v>
+        <v>0.0384</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Es resistente al agua</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>416</v>
+        <v>68</v>
       </c>
       <c r="D120" t="n">
-        <v>0.707106781186548</v>
+        <v>-0.8997785151478557</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>0</v>
+        <v>0.0247</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Es resistente al agua</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.707106781186547</v>
+        <v>1.329140035193965</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>0.0131</v>
+        <v>0</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Con pantalla táctil</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D122" t="n">
-        <v>1.181963330339621</v>
+        <v>-0.7071067811865474</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>0.0535</v>
+        <v>1</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Con pantalla táctil</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>64</v>
+        <v>258</v>
       </c>
       <c r="D123" t="n">
-        <v>-1.005855113373139</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>0.0399</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Peso</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>63</v>
-      </c>
-      <c r="D124" t="n">
-        <v>-0.6245758343210811</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Peso</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>73</v>
-      </c>
-      <c r="D125" t="n">
-        <v>0.4484676173545947</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>0</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Con pantalla táctil</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>57</v>
-      </c>
-      <c r="D126" t="n">
-        <v>-0.7071067811865478</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>1</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Con pantalla táctil</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>270</v>
-      </c>
-      <c r="D127" t="n">
-        <v>0.7071067811865474</v>
+        <v>0.7071067811865478</v>
       </c>
     </row>
   </sheetData>

--- a/data/modelling/atribucion/smartband/df_attr_values_sent.xlsx
+++ b/data/modelling/atribucion/smartband/df_attr_values_sent.xlsx
@@ -425,2061 +425,2427 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>atributo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n_opi_con_sent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>sent</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
         <v>10660.5</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>82</v>
       </c>
-      <c r="D2" t="n">
-        <v>1.055855577370933</v>
+      <c r="E2" t="n">
+        <v>0.6867183994325432</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
         <v>5012.5</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>120</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.2631702585882758</v>
+      <c r="E3" t="n">
+        <v>0.5899300851949941</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
         <v>3385</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>79</v>
       </c>
-      <c r="D4" t="n">
-        <v>-0.6234949305327382</v>
+      <c r="E4" t="n">
+        <v>0.4816666584420749</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
         <v>6444.5</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>103</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.884319034583219</v>
+      <c r="E5" t="n">
+        <v>0.6657734766325888</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
         <v>17689.5</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>60</v>
       </c>
-      <c r="D6" t="n">
-        <v>-1.868746293813093</v>
+      <c r="E6" t="n">
+        <v>0.3296192098542681</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
         <v>1495</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>128</v>
       </c>
-      <c r="D7" t="n">
-        <v>-0.09134947909007532</v>
+      <c r="E7" t="n">
+        <v>0.546642582625221</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
         <v>7930</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>85</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.3802458328934776</v>
+      <c r="E8" t="n">
+        <v>0.6042252250277786</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Xiaomi</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>102</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.899121363459184</v>
+      <c r="E9" t="n">
+        <v>0.6328875445807295</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Imilab</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>43</v>
       </c>
-      <c r="D10" t="n">
-        <v>1.211422833854932</v>
+      <c r="E10" t="n">
+        <v>0.6975344995007392</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="n">
-        <v>-2.013367531221349</v>
+      <c r="E11" t="n">
+        <v>0.02999720903140109</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Microwear</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>31</v>
       </c>
-      <c r="D12" t="n">
-        <v>-0.1939978385867257</v>
+      <c r="E12" t="n">
+        <v>0.4066099427259898</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Amazfit</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>92</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.8929748307109314</v>
+      <c r="E13" t="n">
+        <v>0.6316152014662795</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Smart Bracelet D20</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>10</v>
       </c>
-      <c r="D14" t="n">
-        <v>-0.9875483880610821</v>
+      <c r="E14" t="n">
+        <v>0.2423435800553</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Haylou</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>30</v>
       </c>
-      <c r="D15" t="n">
-        <v>1.040277639773483</v>
+      <c r="E15" t="n">
+        <v>0.6621071426184951</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>DT NO.1</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>28</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.7049543608315747</v>
+      <c r="E16" t="n">
+        <v>0.5926946327448864</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Colmi</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>21</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.9450687180310372</v>
+      <c r="E17" t="n">
+        <v>0.6423987279764921</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Nictom</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>51</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.7317908370472577</v>
+      <c r="E18" t="n">
+        <v>0.5982498306308545</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Mia</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>20</v>
       </c>
-      <c r="D19" t="n">
-        <v>0.9317145594387042</v>
+      <c r="E19" t="n">
+        <v>0.6396343936061825</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>Huawei</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>11</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.1119379998726587</v>
+      <c r="E20" t="n">
+        <v>0.4699392006133662</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>31</v>
       </c>
-      <c r="D21" t="n">
-        <v>0.7289180156124762</v>
+      <c r="E21" t="n">
+        <v>0.5976551515294329</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>Kospet</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>2</v>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>BlueStar</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>Genérica</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>12</v>
       </c>
-      <c r="D24" t="n">
-        <v>-0.467577057749842</v>
+      <c r="E24" t="n">
+        <v>0.3499785620735783</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>Shirajo</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>14</v>
       </c>
-      <c r="D25" t="n">
-        <v>0.1181342791259239</v>
+      <c r="E25" t="n">
+        <v>0.4712218413420506</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>Belmotec</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>3</v>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>Kingwear</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>49</v>
       </c>
-      <c r="D27" t="n">
-        <v>1.191426755195605</v>
+      <c r="E27" t="n">
+        <v>0.6933952759676946</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>SmartWatches</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>29</v>
       </c>
-      <c r="D28" t="n">
-        <v>0.3698076789587996</v>
+      <c r="E28" t="n">
+        <v>0.5233186787759067</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>PSP_BAND</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>8</v>
       </c>
-      <c r="D29" t="n">
-        <v>-1.027783232399406</v>
+      <c r="E29" t="n">
+        <v>0.2340148963483128</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>Gadnic</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>1</v>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>Goufit</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>3</v>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>Netmak</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>16</v>
       </c>
-      <c r="D32" t="n">
-        <v>0.05049564068011295</v>
+      <c r="E32" t="n">
+        <v>0.457220523945382</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>Honor</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>10</v>
       </c>
-      <c r="D33" t="n">
-        <v>-0.276023949561949</v>
+      <c r="E33" t="n">
+        <v>0.389630393152434</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>Motorola</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>1</v>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>Noga</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>19</v>
       </c>
-      <c r="D35" t="n">
-        <v>-0.3089983889080233</v>
+      <c r="E35" t="n">
+        <v>0.3828046260780203</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>Daikon</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>3</v>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>Mibro</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>2</v>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>Daza</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>HiFuture</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>Ruffo</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>1</v>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>HDT8</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>4</v>
       </c>
-      <c r="D41" t="n">
-        <v>-1.928617288657353</v>
+      <c r="E41" t="n">
+        <v>0.04754065864613308</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>8</v>
       </c>
-      <c r="D42" t="n">
-        <v>-1.231489629931741</v>
+      <c r="E42" t="n">
+        <v>0.1918473129504419</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>Doogee</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>Level Up</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>Rohs</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>ISANFIT</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>Veryfit</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
         <v>4</v>
       </c>
-      <c r="D47" t="n">
-        <v>-1.70273178450078</v>
+      <c r="E47" t="n">
+        <v>0.09429935621418792</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>Phull</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>Haxly</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>Soul</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>Integra</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
         <v>17</v>
       </c>
-      <c r="D52" t="n">
-        <v>0.8998556324164519</v>
+      <c r="E52" t="n">
+        <v>0.6330395395493075</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>Uprint</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>WICKPRO</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>ONCELULAR2</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>T-Go</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
         <v>8</v>
       </c>
-      <c r="D57" t="n">
-        <v>-0.6897660554308787</v>
+      <c r="E57" t="n">
+        <v>0.303985047862434</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>IWO</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>JAZAK</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
         <v>1</v>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>LCS</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
         <v>1</v>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>Tressa</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>WickPro</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B63" t="inlineStr">
         <is>
           <t>Stone</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>Suono</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B65" t="inlineStr">
         <is>
           <t>SLA</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B66" t="inlineStr">
         <is>
           <t>Kanji</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>Solana</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B68" t="inlineStr">
         <is>
           <t>X8</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B69" t="inlineStr">
         <is>
           <t>LEZAYA</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B70" t="inlineStr">
         <is>
           <t>Reloj Smartband M6</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B71" t="inlineStr">
         <is>
           <t>SMART WATCH BRACELET</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="n">
+      <c r="A72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B72" t="n">
         <v>185</v>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Capacidad de la batería</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="D72" t="n">
         <v>119</v>
       </c>
-      <c r="D72" t="n">
-        <v>0.5128526212504075</v>
+      <c r="E72" t="n">
+        <v>0.156878134931199</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
+      <c r="A73" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" t="n">
         <v>142</v>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Capacidad de la batería</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="D73" t="n">
         <v>70</v>
       </c>
-      <c r="D73" t="n">
-        <v>-0.04779369282183864</v>
+      <c r="E73" t="n">
+        <v>0.0966122301475693</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
+      <c r="A74" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B74" t="n">
         <v>375</v>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Capacidad de la batería</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="D74" t="n">
         <v>95</v>
       </c>
-      <c r="D74" t="n">
-        <v>0.7393994135284503</v>
+      <c r="E74" t="n">
+        <v>0.1812304709223099</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B75" t="n">
         <v>296</v>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Capacidad de la batería</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="D75" t="n">
         <v>61</v>
       </c>
-      <c r="D75" t="n">
-        <v>-0.2738141743229234</v>
+      <c r="E75" t="n">
+        <v>0.07231646920988263</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
+      <c r="A76" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B76" t="n">
         <v>240</v>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Capacidad de la batería</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="D76" t="n">
         <v>102</v>
       </c>
-      <c r="D76" t="n">
-        <v>0.8911370887423397</v>
+      <c r="E76" t="n">
+        <v>0.1975413037183161</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
+      <c r="A77" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B77" t="n">
         <v>82.5</v>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Capacidad de la batería</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="D77" t="n">
         <v>39</v>
       </c>
-      <c r="D77" t="n">
-        <v>-1.821781256376436</v>
+      <c r="E77" t="n">
+        <v>-0.09408012421034714</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
+      <c r="A78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B78" t="n">
         <v>168</v>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Duración de la batería</t>
         </is>
       </c>
-      <c r="C78" t="n">
+      <c r="D78" t="n">
         <v>91</v>
       </c>
-      <c r="D78" t="n">
-        <v>0.5595477917045737</v>
+      <c r="E78" t="n">
+        <v>0.2348293408662897</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
+      <c r="A79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B79" t="n">
         <v>288</v>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Duración de la batería</t>
         </is>
       </c>
-      <c r="C79" t="n">
+      <c r="D79" t="n">
         <v>111</v>
       </c>
-      <c r="D79" t="n">
-        <v>0.2719995332055359</v>
+      <c r="E79" t="n">
+        <v>0.199780556655212</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
+      <c r="A80" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B80" t="n">
         <v>468</v>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Duración de la batería</t>
         </is>
       </c>
-      <c r="C80" t="n">
+      <c r="D80" t="n">
         <v>115</v>
       </c>
-      <c r="D80" t="n">
-        <v>0.6489298281825794</v>
+      <c r="E80" t="n">
+        <v>0.2457239702589931</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
+      <c r="A81" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B81" t="n">
         <v>56</v>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Duración de la batería</t>
         </is>
       </c>
-      <c r="C81" t="n">
+      <c r="D81" t="n">
         <v>25</v>
       </c>
-      <c r="D81" t="n">
-        <v>-1.480477153092689</v>
+      <c r="E81" t="n">
+        <v>-0.01382594381057517</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
+      <c r="A82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B82" t="n">
         <v>40.64</v>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C82" t="n">
+      <c r="D82" t="n">
         <v>66</v>
       </c>
-      <c r="D82" t="n">
-        <v>0.8238185741505839</v>
+      <c r="E82" t="n">
+        <v>0.4255919605180238</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
+      <c r="A83" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B83" t="n">
         <v>30.099</v>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C83" t="n">
+      <c r="D83" t="n">
         <v>89</v>
       </c>
-      <c r="D83" t="n">
-        <v>0.4358885755785805</v>
+      <c r="E83" t="n">
+        <v>0.3562763701769225</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
+      <c r="A84" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B84" t="n">
         <v>43.22499999999999</v>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C84" t="n">
+      <c r="D84" t="n">
         <v>16</v>
       </c>
-      <c r="D84" t="n">
-        <v>-0.6770457472582471</v>
+      <c r="E84" t="n">
+        <v>0.1574165246319025</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
+      <c r="A85" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B85" t="n">
         <v>34.163</v>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C85" t="n">
+      <c r="D85" t="n">
         <v>55</v>
       </c>
-      <c r="D85" t="n">
-        <v>-0.484824784060277</v>
+      <c r="E85" t="n">
+        <v>0.191762694273458</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
+      <c r="A86" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B86" t="n">
         <v>37.33799999999999</v>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C86" t="n">
+      <c r="D86" t="n">
         <v>50</v>
       </c>
-      <c r="D86" t="n">
-        <v>1.261251925820264</v>
+      <c r="E86" t="n">
+        <v>0.5037528429387796</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
+      <c r="A87" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B87" t="n">
         <v>19.335</v>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C87" t="n">
+      <c r="D87" t="n">
         <v>13</v>
       </c>
-      <c r="D87" t="n">
-        <v>-1.359088544230904</v>
+      <c r="E87" t="n">
+        <v>0.03554866371863861</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
+      <c r="A88" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B88" t="n">
         <v>52.479</v>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C88" t="n">
+      <c r="D88" t="n">
         <v>2</v>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B89" t="inlineStr">
         <is>
           <t>AMOLED</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Tipo de pantalla</t>
         </is>
       </c>
-      <c r="C89" t="n">
+      <c r="D89" t="n">
         <v>123</v>
       </c>
-      <c r="D89" t="n">
-        <v>0.8989412771858279</v>
+      <c r="E89" t="n">
+        <v>0.4780949458436305</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B90" t="inlineStr">
         <is>
           <t>LCD TFT</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Tipo de pantalla</t>
         </is>
       </c>
-      <c r="C90" t="n">
+      <c r="D90" t="n">
         <v>76</v>
       </c>
-      <c r="D90" t="n">
-        <v>0.8175982199607241</v>
+      <c r="E90" t="n">
+        <v>0.4614161403084724</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B91" t="inlineStr">
         <is>
           <t>LCD IPS</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Tipo de pantalla</t>
         </is>
       </c>
-      <c r="C91" t="n">
+      <c r="D91" t="n">
         <v>19</v>
       </c>
-      <c r="D91" t="n">
-        <v>-0.6998655058010271</v>
+      <c r="E91" t="n">
+        <v>0.1502711790538601</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B92" t="inlineStr">
         <is>
           <t>LTPS</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Tipo de pantalla</t>
         </is>
       </c>
-      <c r="C92" t="n">
+      <c r="D92" t="n">
         <v>2</v>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B93" t="inlineStr">
         <is>
           <t>SAMOLED</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Tipo de pantalla</t>
         </is>
       </c>
-      <c r="C93" t="n">
+      <c r="D93" t="n">
         <v>9</v>
       </c>
-      <c r="D93" t="n">
-        <v>-1.016673991345525</v>
+      <c r="E93" t="n">
+        <v>0.08531189054738048</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B94" t="inlineStr">
         <is>
           <t>Táctil</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Tipo de pantalla</t>
         </is>
       </c>
-      <c r="C94" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B95" t="inlineStr">
         <is>
           <t>IPS</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Tipo de pantalla</t>
         </is>
       </c>
-      <c r="C95" t="n">
+      <c r="D95" t="n">
         <v>6</v>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B96" t="inlineStr">
         <is>
           <t>LCD</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Tipo de pantalla</t>
         </is>
       </c>
-      <c r="C96" t="n">
+      <c r="D96" t="n">
         <v>5</v>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B97" t="inlineStr">
         <is>
           <t>OLED</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Tipo de pantalla</t>
         </is>
       </c>
-      <c r="C97" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B98" t="inlineStr">
         <is>
           <t>TFT</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Tipo de pantalla</t>
         </is>
       </c>
-      <c r="C98" t="n">
+      <c r="D98" t="n">
         <v>4</v>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B99" t="inlineStr">
         <is>
           <t>Silicona</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C99" t="n">
+      <c r="D99" t="n">
         <v>244</v>
       </c>
-      <c r="D99" t="n">
-        <v>1.234950459141323</v>
+      <c r="E99" t="n">
+        <v>0.463394323703906</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B100" t="inlineStr">
         <is>
           <t>TPU/Aleación de aluminio</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C100" t="n">
+      <c r="D100" t="n">
         <v>11</v>
       </c>
-      <c r="D100" t="n">
-        <v>-0.1232981474784827</v>
+      <c r="E100" t="n">
+        <v>0.1821612299426851</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B101" t="inlineStr">
         <is>
           <t>Elastómero termoplástico/Aleación de aluminio</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C101" t="n">
+      <c r="D101" t="n">
         <v>11</v>
       </c>
-      <c r="D101" t="n">
-        <v>-0.6520726408526637</v>
+      <c r="E101" t="n">
+        <v>0.07267546573952768</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B102" t="inlineStr">
         <is>
           <t>TPU</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C102" t="n">
+      <c r="D102" t="n">
         <v>36</v>
       </c>
-      <c r="D102" t="n">
-        <v>0.001251172932257644</v>
+      <c r="E102" t="n">
+        <v>0.2079498746239712</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B103" t="inlineStr">
         <is>
           <t>Caucho de silicona</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C103" t="n">
+      <c r="D103" t="n">
         <v>17</v>
       </c>
-      <c r="D103" t="n">
-        <v>-0.3060680595009452</v>
+      <c r="E103" t="n">
+        <v>0.1443176808648312</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B104" t="inlineStr">
         <is>
           <t>Fluoroelastómero</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C104" t="n">
+      <c r="D104" t="n">
         <v>17</v>
       </c>
-      <c r="D104" t="n">
-        <v>0.4858723588604913</v>
+      <c r="E104" t="n">
+        <v>0.3082934455700955</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B105" t="inlineStr">
         <is>
           <t>Cuero</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C105" t="n">
+      <c r="D105" t="n">
         <v>11</v>
       </c>
-      <c r="D105" t="n">
-        <v>-0.1500954042005175</v>
+      <c r="E105" t="n">
+        <v>0.1766127056331284</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B106" t="inlineStr">
         <is>
           <t>Acero inoxidable</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C106" t="n">
+      <c r="D106" t="n">
         <v>35</v>
       </c>
-      <c r="D106" t="n">
-        <v>2.266885902735144</v>
+      <c r="E106" t="n">
+        <v>0.6770624224225845</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B107" t="inlineStr">
         <is>
           <t>Caucho</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B108" t="inlineStr">
         <is>
           <t>Plástico</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C108" t="n">
+      <c r="D108" t="n">
         <v>13</v>
       </c>
-      <c r="D108" t="n">
-        <v>-0.8510639781586837</v>
+      <c r="E108" t="n">
+        <v>0.03147317836039584</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B109" t="inlineStr">
         <is>
           <t>Metal</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C109" t="n">
-        <v>0</v>
-      </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B110" t="inlineStr">
         <is>
           <t>Acero inoxidable/Silicona</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C110" t="n">
+      <c r="D110" t="n">
         <v>6</v>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B111" t="inlineStr">
         <is>
           <t>1ra Cuero/TPU - 2da Silicona negra</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C111" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B112" t="inlineStr">
         <is>
           <t>1ra Metal - 2da Silicona</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C112" t="n">
-        <v>0</v>
-      </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B113" t="inlineStr">
         <is>
           <t>Cuero Genuino</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C113" t="n">
+      <c r="D113" t="n">
         <v>7</v>
       </c>
-      <c r="D113" t="n">
-        <v>-0.9850195854167664</v>
+      <c r="E113" t="n">
+        <v>0.003736908525665338</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B114" t="inlineStr">
         <is>
           <t>Rosa / negra</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C114" t="n">
+      <c r="D114" t="n">
         <v>7</v>
       </c>
-      <c r="D114" t="n">
-        <v>-0.9213420780611582</v>
+      <c r="E114" t="n">
+        <v>0.01692169834200662</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B115" t="inlineStr">
         <is>
           <t>Resina</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="C115" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="n">
+      <c r="A116" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B116" t="n">
         <v>1</v>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>Es resistente al agua</t>
         </is>
       </c>
-      <c r="C116" t="n">
+      <c r="D116" t="n">
         <v>391</v>
       </c>
-      <c r="D116" t="n">
-        <v>0.7071067811865475</v>
+      <c r="E116" t="n">
+        <v>0.4661149878034115</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="n">
-        <v>0</v>
-      </c>
-      <c r="B117" t="inlineStr">
+      <c r="A117" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" t="inlineStr">
         <is>
           <t>Es resistente al agua</t>
         </is>
       </c>
-      <c r="C117" t="n">
+      <c r="D117" t="n">
         <v>55</v>
       </c>
-      <c r="D117" t="n">
-        <v>-0.7071067811865475</v>
+      <c r="E117" t="n">
+        <v>0.2968168254415011</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="n">
+      <c r="A118" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B118" t="n">
         <v>0.0126</v>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="C118" t="n">
+      <c r="D118" t="n">
         <v>60</v>
       </c>
-      <c r="D118" t="n">
-        <v>0.1925106771872289</v>
+      <c r="E118" t="n">
+        <v>0.4578263312070821</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="n">
+      <c r="A119" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B119" t="n">
         <v>0.054</v>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="C119" t="n">
+      <c r="D119" t="n">
         <v>58</v>
       </c>
-      <c r="D119" t="n">
-        <v>-0.6218721972333383</v>
+      <c r="E119" t="n">
+        <v>0.425148634731482</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="n">
+      <c r="A120" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B120" t="n">
         <v>0.0384</v>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="C120" t="n">
+      <c r="D120" t="n">
         <v>68</v>
       </c>
-      <c r="D120" t="n">
-        <v>-0.8997785151478557</v>
+      <c r="E120" t="n">
+        <v>0.4139974445595084</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="n">
+      <c r="A121" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B121" t="n">
         <v>0.0247</v>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="C121" t="n">
+      <c r="D121" t="n">
         <v>61</v>
       </c>
-      <c r="D121" t="n">
-        <v>1.329140035193965</v>
+      <c r="E121" t="n">
+        <v>0.5034343987792632</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="n">
-        <v>0</v>
-      </c>
-      <c r="B122" t="inlineStr">
+      <c r="A122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" t="inlineStr">
         <is>
           <t>Con pantalla táctil</t>
         </is>
       </c>
-      <c r="C122" t="n">
+      <c r="D122" t="n">
         <v>57</v>
       </c>
-      <c r="D122" t="n">
-        <v>-0.7071067811865474</v>
+      <c r="E122" t="n">
+        <v>0.2312934490571912</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="n">
+      <c r="A123" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" t="inlineStr">
         <is>
           <t>Con pantalla táctil</t>
         </is>
       </c>
-      <c r="C123" t="n">
+      <c r="D123" t="n">
         <v>258</v>
       </c>
-      <c r="D123" t="n">
-        <v>0.7071067811865478</v>
+      <c r="E123" t="n">
+        <v>0.3348798819290331</v>
       </c>
     </row>
   </sheetData>
